--- a/data/H131_20260622_16.xlsx
+++ b/data/H131_20260622_16.xlsx
@@ -593,7 +593,7 @@
         <v>1074.0</v>
       </c>
       <c r="J4" s="2">
-        <v>866.0</v>
+        <v>882.0</v>
       </c>
       <c r="K4" s="2">
         <v>1.0</v>
@@ -605,25 +605,25 @@
         <v>0.0</v>
       </c>
       <c r="N4" s="2">
-        <v>866.0</v>
+        <v>882.0</v>
       </c>
       <c r="O4" s="2">
-        <v>505.0</v>
+        <v>518.0</v>
       </c>
       <c r="P4" s="2">
-        <v>361.0</v>
+        <v>364.0</v>
       </c>
       <c r="Q4" s="2">
         <v>0.0</v>
       </c>
       <c r="R4" s="2">
-        <v>55.0</v>
+        <v>58.0</v>
       </c>
       <c r="S4" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T4" s="2">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
       <c r="U4" s="2">
         <v>0.0</v>
@@ -632,7 +632,7 @@
         <v>0.0</v>
       </c>
       <c r="W4" s="2">
-        <v>60.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         <v>667.0</v>
       </c>
       <c r="J5" s="2">
-        <v>630.0</v>
+        <v>631.0</v>
       </c>
       <c r="K5" s="2">
         <v>1.0</v>
@@ -676,13 +676,13 @@
         <v>0.0</v>
       </c>
       <c r="N5" s="2">
-        <v>630.0</v>
+        <v>631.0</v>
       </c>
       <c r="O5" s="2">
         <v>333.0</v>
       </c>
       <c r="P5" s="2">
-        <v>295.0</v>
+        <v>296.0</v>
       </c>
       <c r="Q5" s="2">
         <v>2.0</v>
@@ -735,7 +735,7 @@
         <v>929.0</v>
       </c>
       <c r="J6" s="2">
-        <v>856.0</v>
+        <v>859.0</v>
       </c>
       <c r="K6" s="2">
         <v>1.0</v>
@@ -747,16 +747,16 @@
         <v>0.0</v>
       </c>
       <c r="N6" s="2">
-        <v>856.0</v>
+        <v>859.0</v>
       </c>
       <c r="O6" s="2">
         <v>461.0</v>
       </c>
       <c r="P6" s="2">
-        <v>395.0</v>
+        <v>397.0</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R6" s="2">
         <v>37.0</v>
@@ -877,7 +877,7 @@
         <v>711.0</v>
       </c>
       <c r="J8" s="2">
-        <v>630.0</v>
+        <v>633.0</v>
       </c>
       <c r="K8" s="2">
         <v>1.0</v>
@@ -889,13 +889,13 @@
         <v>0.0</v>
       </c>
       <c r="N8" s="2">
-        <v>630.0</v>
+        <v>633.0</v>
       </c>
       <c r="O8" s="2">
-        <v>374.0</v>
+        <v>375.0</v>
       </c>
       <c r="P8" s="2">
-        <v>255.0</v>
+        <v>257.0</v>
       </c>
       <c r="Q8" s="2">
         <v>1.0</v>
@@ -1090,7 +1090,7 @@
         <v>561.0</v>
       </c>
       <c r="J11" s="2">
-        <v>553.0</v>
+        <v>554.0</v>
       </c>
       <c r="K11" s="2">
         <v>1.0</v>
@@ -1102,10 +1102,10 @@
         <v>0.0</v>
       </c>
       <c r="N11" s="2">
-        <v>553.0</v>
+        <v>554.0</v>
       </c>
       <c r="O11" s="2">
-        <v>356.0</v>
+        <v>357.0</v>
       </c>
       <c r="P11" s="2">
         <v>197.0</v>
@@ -1185,7 +1185,7 @@
         <v>5.0</v>
       </c>
       <c r="R12" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="S12" s="2">
         <v>8.0</v>
@@ -1200,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="W12" s="2">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="13">
@@ -1303,7 +1303,7 @@
         <v>1342.0</v>
       </c>
       <c r="J14" s="2">
-        <v>1229.0</v>
+        <v>1242.0</v>
       </c>
       <c r="K14" s="2">
         <v>1.0</v>
@@ -1315,16 +1315,16 @@
         <v>0.0</v>
       </c>
       <c r="N14" s="2">
-        <v>1229.0</v>
+        <v>1242.0</v>
       </c>
       <c r="O14" s="2">
-        <v>691.0</v>
+        <v>698.0</v>
       </c>
       <c r="P14" s="2">
-        <v>536.0</v>
+        <v>541.0</v>
       </c>
       <c r="Q14" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="R14" s="2">
         <v>37.0</v>
@@ -1336,13 +1336,13 @@
         <v>4.0</v>
       </c>
       <c r="U14" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="V14" s="2">
         <v>0.0</v>
       </c>
       <c r="W14" s="2">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="15">
@@ -1404,7 +1404,7 @@
         <v>12.0</v>
       </c>
       <c r="T15" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U15" s="2">
         <v>15.0</v>
@@ -1413,7 +1413,7 @@
         <v>0.0</v>
       </c>
       <c r="W15" s="2">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="16">
@@ -1516,7 +1516,7 @@
         <v>829.0</v>
       </c>
       <c r="J17" s="2">
-        <v>755.0</v>
+        <v>756.0</v>
       </c>
       <c r="K17" s="2">
         <v>1.0</v>
@@ -1528,10 +1528,10 @@
         <v>0.0</v>
       </c>
       <c r="N17" s="2">
-        <v>755.0</v>
+        <v>756.0</v>
       </c>
       <c r="O17" s="2">
-        <v>417.0</v>
+        <v>418.0</v>
       </c>
       <c r="P17" s="2">
         <v>336.0</v>
@@ -2013,7 +2013,7 @@
         <v>1296.0</v>
       </c>
       <c r="J24" s="2">
-        <v>1201.0</v>
+        <v>1214.0</v>
       </c>
       <c r="K24" s="2">
         <v>1.0</v>
@@ -2025,25 +2025,25 @@
         <v>0.0</v>
       </c>
       <c r="N24" s="2">
-        <v>1201.0</v>
+        <v>1214.0</v>
       </c>
       <c r="O24" s="2">
-        <v>731.0</v>
+        <v>740.0</v>
       </c>
       <c r="P24" s="2">
-        <v>451.0</v>
+        <v>452.0</v>
       </c>
       <c r="Q24" s="2">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
       <c r="R24" s="2">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
       <c r="S24" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="T24" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="U24" s="2">
         <v>1.0</v>
@@ -2052,7 +2052,7 @@
         <v>0.0</v>
       </c>
       <c r="W24" s="2">
-        <v>39.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -2297,7 +2297,7 @@
         <v>1349.0</v>
       </c>
       <c r="J28" s="2">
-        <v>1152.0</v>
+        <v>1164.0</v>
       </c>
       <c r="K28" s="2">
         <v>1.0</v>
@@ -2309,13 +2309,13 @@
         <v>0.0</v>
       </c>
       <c r="N28" s="2">
-        <v>1152.0</v>
+        <v>1164.0</v>
       </c>
       <c r="O28" s="2">
-        <v>651.0</v>
+        <v>660.0</v>
       </c>
       <c r="P28" s="2">
-        <v>499.0</v>
+        <v>502.0</v>
       </c>
       <c r="Q28" s="2">
         <v>2.0</v>
@@ -2368,7 +2368,7 @@
         <v>1280.0</v>
       </c>
       <c r="J29" s="2">
-        <v>874.0</v>
+        <v>938.0</v>
       </c>
       <c r="K29" s="2">
         <v>1.0</v>
@@ -2380,19 +2380,19 @@
         <v>0.0</v>
       </c>
       <c r="N29" s="2">
-        <v>874.0</v>
+        <v>938.0</v>
       </c>
       <c r="O29" s="2">
-        <v>329.0</v>
+        <v>333.0</v>
       </c>
       <c r="P29" s="2">
-        <v>413.0</v>
+        <v>414.0</v>
       </c>
       <c r="Q29" s="2">
-        <v>132.0</v>
+        <v>191.0</v>
       </c>
       <c r="R29" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="S29" s="2">
         <v>0.0</v>
@@ -2407,7 +2407,7 @@
         <v>0.0</v>
       </c>
       <c r="W29" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -2439,7 +2439,7 @@
         <v>258.0</v>
       </c>
       <c r="J30" s="2">
-        <v>250.0</v>
+        <v>251.0</v>
       </c>
       <c r="K30" s="2">
         <v>1.0</v>
@@ -2451,10 +2451,10 @@
         <v>0.0</v>
       </c>
       <c r="N30" s="2">
-        <v>250.0</v>
+        <v>251.0</v>
       </c>
       <c r="O30" s="2">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
       <c r="P30" s="2">
         <v>87.0</v>
@@ -2581,7 +2581,7 @@
         <v>1143.0</v>
       </c>
       <c r="J32" s="2">
-        <v>919.0</v>
+        <v>994.0</v>
       </c>
       <c r="K32" s="2">
         <v>1.0</v>
@@ -2593,34 +2593,34 @@
         <v>0.0</v>
       </c>
       <c r="N32" s="2">
-        <v>919.0</v>
+        <v>994.0</v>
       </c>
       <c r="O32" s="2">
-        <v>439.0</v>
+        <v>492.0</v>
       </c>
       <c r="P32" s="2">
-        <v>450.0</v>
+        <v>470.0</v>
       </c>
       <c r="Q32" s="2">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="R32" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="S32" s="2">
         <v>4.0</v>
       </c>
       <c r="T32" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="U32" s="2">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="V32" s="2">
         <v>0.0</v>
       </c>
       <c r="W32" s="2">
-        <v>34.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
@@ -2865,7 +2865,7 @@
         <v>1103.0</v>
       </c>
       <c r="J36" s="2">
-        <v>931.0</v>
+        <v>969.0</v>
       </c>
       <c r="K36" s="2">
         <v>1.0</v>
@@ -2877,16 +2877,16 @@
         <v>0.0</v>
       </c>
       <c r="N36" s="2">
-        <v>931.0</v>
+        <v>969.0</v>
       </c>
       <c r="O36" s="2">
-        <v>468.0</v>
+        <v>481.0</v>
       </c>
       <c r="P36" s="2">
-        <v>443.0</v>
+        <v>466.0</v>
       </c>
       <c r="Q36" s="2">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="R36" s="2">
         <v>45.0</v>
@@ -2895,7 +2895,7 @@
         <v>24.0</v>
       </c>
       <c r="T36" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="U36" s="2">
         <v>11.0</v>
@@ -2904,7 +2904,7 @@
         <v>0.0</v>
       </c>
       <c r="W36" s="2">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
@@ -3007,7 +3007,7 @@
         <v>1123.0</v>
       </c>
       <c r="J38" s="2">
-        <v>1045.0</v>
+        <v>1050.0</v>
       </c>
       <c r="K38" s="2">
         <v>1.0</v>
@@ -3019,16 +3019,16 @@
         <v>0.0</v>
       </c>
       <c r="N38" s="2">
-        <v>1045.0</v>
+        <v>1050.0</v>
       </c>
       <c r="O38" s="2">
-        <v>599.0</v>
+        <v>602.0</v>
       </c>
       <c r="P38" s="2">
-        <v>427.0</v>
+        <v>428.0</v>
       </c>
       <c r="Q38" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="R38" s="2">
         <v>37.0</v>
@@ -3220,7 +3220,7 @@
         <v>1244.0</v>
       </c>
       <c r="J41" s="2">
-        <v>1154.0</v>
+        <v>1175.0</v>
       </c>
       <c r="K41" s="2">
         <v>1.0</v>
@@ -3232,13 +3232,13 @@
         <v>0.0</v>
       </c>
       <c r="N41" s="2">
-        <v>1154.0</v>
+        <v>1175.0</v>
       </c>
       <c r="O41" s="2">
-        <v>624.0</v>
+        <v>634.0</v>
       </c>
       <c r="P41" s="2">
-        <v>530.0</v>
+        <v>541.0</v>
       </c>
       <c r="Q41" s="2">
         <v>0.0</v>
@@ -3291,7 +3291,7 @@
         <v>1005.0</v>
       </c>
       <c r="J42" s="2">
-        <v>861.0</v>
+        <v>875.0</v>
       </c>
       <c r="K42" s="2">
         <v>1.0</v>
@@ -3303,22 +3303,22 @@
         <v>0.0</v>
       </c>
       <c r="N42" s="2">
-        <v>861.0</v>
+        <v>875.0</v>
       </c>
       <c r="O42" s="2">
-        <v>545.0</v>
+        <v>554.0</v>
       </c>
       <c r="P42" s="2">
-        <v>315.0</v>
+        <v>319.0</v>
       </c>
       <c r="Q42" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R42" s="2">
-        <v>30.0</v>
+        <v>34.0</v>
       </c>
       <c r="S42" s="2">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="T42" s="2">
         <v>1.0</v>
@@ -3330,7 +3330,7 @@
         <v>0.0</v>
       </c>
       <c r="W42" s="2">
-        <v>35.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
@@ -3362,7 +3362,7 @@
         <v>1022.0</v>
       </c>
       <c r="J43" s="2">
-        <v>956.0</v>
+        <v>965.0</v>
       </c>
       <c r="K43" s="2">
         <v>1.0</v>
@@ -3374,13 +3374,13 @@
         <v>0.0</v>
       </c>
       <c r="N43" s="2">
-        <v>956.0</v>
+        <v>965.0</v>
       </c>
       <c r="O43" s="2">
-        <v>499.0</v>
+        <v>501.0</v>
       </c>
       <c r="P43" s="2">
-        <v>445.0</v>
+        <v>452.0</v>
       </c>
       <c r="Q43" s="2">
         <v>12.0</v>
@@ -3661,13 +3661,13 @@
         <v>759.0</v>
       </c>
       <c r="O47" s="2">
-        <v>403.0</v>
+        <v>404.0</v>
       </c>
       <c r="P47" s="2">
         <v>336.0</v>
       </c>
       <c r="Q47" s="2">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="R47" s="2">
         <v>23.0</v>
@@ -3717,7 +3717,7 @@
         <v>1102.0</v>
       </c>
       <c r="J48" s="2">
-        <v>1009.0</v>
+        <v>1038.0</v>
       </c>
       <c r="K48" s="2">
         <v>1.0</v>
@@ -3729,25 +3729,25 @@
         <v>0.0</v>
       </c>
       <c r="N48" s="2">
-        <v>1009.0</v>
+        <v>1038.0</v>
       </c>
       <c r="O48" s="2">
-        <v>608.0</v>
+        <v>623.0</v>
       </c>
       <c r="P48" s="2">
-        <v>401.0</v>
+        <v>410.0</v>
       </c>
       <c r="Q48" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="R48" s="2">
         <v>30.0</v>
       </c>
       <c r="S48" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="T48" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="U48" s="2">
         <v>10.0</v>
@@ -3756,7 +3756,7 @@
         <v>0.0</v>
       </c>
       <c r="W48" s="2">
-        <v>46.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
@@ -3930,7 +3930,7 @@
         <v>878.0</v>
       </c>
       <c r="J51" s="2">
-        <v>806.0</v>
+        <v>811.0</v>
       </c>
       <c r="K51" s="2">
         <v>1.0</v>
@@ -3942,13 +3942,13 @@
         <v>0.0</v>
       </c>
       <c r="N51" s="2">
-        <v>806.0</v>
+        <v>811.0</v>
       </c>
       <c r="O51" s="2">
-        <v>383.0</v>
+        <v>386.0</v>
       </c>
       <c r="P51" s="2">
-        <v>423.0</v>
+        <v>425.0</v>
       </c>
       <c r="Q51" s="2">
         <v>0.0</v>
@@ -4285,7 +4285,7 @@
         <v>615.0</v>
       </c>
       <c r="J56" s="2">
-        <v>596.0</v>
+        <v>597.0</v>
       </c>
       <c r="K56" s="2">
         <v>1.0</v>
@@ -4297,10 +4297,10 @@
         <v>0.0</v>
       </c>
       <c r="N56" s="2">
-        <v>596.0</v>
+        <v>597.0</v>
       </c>
       <c r="O56" s="2">
-        <v>303.0</v>
+        <v>304.0</v>
       </c>
       <c r="P56" s="2">
         <v>293.0</v>
@@ -4584,13 +4584,13 @@
         <v>662.0</v>
       </c>
       <c r="O60" s="2">
-        <v>295.0</v>
+        <v>296.0</v>
       </c>
       <c r="P60" s="2">
         <v>364.0</v>
       </c>
       <c r="Q60" s="2">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="R60" s="2">
         <v>12.0</v>
@@ -5093,7 +5093,7 @@
         <v>61.0</v>
       </c>
       <c r="S67" s="2">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="T67" s="2">
         <v>0.0</v>
@@ -5105,7 +5105,7 @@
         <v>0.0</v>
       </c>
       <c r="W67" s="2">
-        <v>79.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
@@ -5232,7 +5232,7 @@
         <v>11.0</v>
       </c>
       <c r="R69" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="S69" s="2">
         <v>2.0</v>
@@ -5247,7 +5247,7 @@
         <v>0.0</v>
       </c>
       <c r="W69" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
@@ -5776,7 +5776,7 @@
         <v>792.0</v>
       </c>
       <c r="J77" s="2">
-        <v>703.0</v>
+        <v>724.0</v>
       </c>
       <c r="K77" s="2">
         <v>1.0</v>
@@ -5788,19 +5788,19 @@
         <v>0.0</v>
       </c>
       <c r="N77" s="2">
-        <v>703.0</v>
+        <v>724.0</v>
       </c>
       <c r="O77" s="2">
-        <v>198.0</v>
+        <v>207.0</v>
       </c>
       <c r="P77" s="2">
-        <v>345.0</v>
+        <v>353.0</v>
       </c>
       <c r="Q77" s="2">
-        <v>160.0</v>
+        <v>164.0</v>
       </c>
       <c r="R77" s="2">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="S77" s="2">
         <v>1.0</v>
@@ -5815,7 +5815,7 @@
         <v>0.0</v>
       </c>
       <c r="W77" s="2">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
@@ -5847,7 +5847,7 @@
         <v>1275.0</v>
       </c>
       <c r="J78" s="2">
-        <v>1071.0</v>
+        <v>1093.0</v>
       </c>
       <c r="K78" s="2">
         <v>1.0</v>
@@ -5859,34 +5859,34 @@
         <v>0.0</v>
       </c>
       <c r="N78" s="2">
-        <v>1071.0</v>
+        <v>1093.0</v>
       </c>
       <c r="O78" s="2">
-        <v>484.0</v>
+        <v>495.0</v>
       </c>
       <c r="P78" s="2">
-        <v>587.0</v>
+        <v>598.0</v>
       </c>
       <c r="Q78" s="2">
         <v>0.0</v>
       </c>
       <c r="R78" s="2">
-        <v>51.0</v>
+        <v>54.0</v>
       </c>
       <c r="S78" s="2">
-        <v>54.0</v>
+        <v>56.0</v>
       </c>
       <c r="T78" s="2">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="U78" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="V78" s="2">
         <v>1.0</v>
       </c>
       <c r="W78" s="2">
-        <v>116.0</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
@@ -5918,7 +5918,7 @@
         <v>787.0</v>
       </c>
       <c r="J79" s="2">
-        <v>721.0</v>
+        <v>724.0</v>
       </c>
       <c r="K79" s="2">
         <v>1.0</v>
@@ -5930,10 +5930,10 @@
         <v>0.0</v>
       </c>
       <c r="N79" s="2">
-        <v>721.0</v>
+        <v>724.0</v>
       </c>
       <c r="O79" s="2">
-        <v>454.0</v>
+        <v>457.0</v>
       </c>
       <c r="P79" s="2">
         <v>267.0</v>
@@ -5945,7 +5945,7 @@
         <v>26.0</v>
       </c>
       <c r="S79" s="2">
-        <v>26.0</v>
+        <v>29.0</v>
       </c>
       <c r="T79" s="2">
         <v>8.0</v>
@@ -5957,7 +5957,7 @@
         <v>0.0</v>
       </c>
       <c r="W79" s="2">
-        <v>60.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
@@ -6131,7 +6131,7 @@
         <v>1157.0</v>
       </c>
       <c r="J82" s="2">
-        <v>989.0</v>
+        <v>1017.0</v>
       </c>
       <c r="K82" s="2">
         <v>1.0</v>
@@ -6143,25 +6143,25 @@
         <v>0.0</v>
       </c>
       <c r="N82" s="2">
-        <v>989.0</v>
+        <v>1017.0</v>
       </c>
       <c r="O82" s="2">
-        <v>509.0</v>
+        <v>521.0</v>
       </c>
       <c r="P82" s="2">
-        <v>480.0</v>
+        <v>487.0</v>
       </c>
       <c r="Q82" s="2">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="R82" s="2">
-        <v>60.0</v>
+        <v>70.0</v>
       </c>
       <c r="S82" s="2">
-        <v>45.0</v>
+        <v>57.0</v>
       </c>
       <c r="T82" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U82" s="2">
         <v>0.0</v>
@@ -6170,7 +6170,7 @@
         <v>0.0</v>
       </c>
       <c r="W82" s="2">
-        <v>105.0</v>
+        <v>128.0</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
@@ -6202,7 +6202,7 @@
         <v>1127.0</v>
       </c>
       <c r="J83" s="2">
-        <v>1036.0</v>
+        <v>1042.0</v>
       </c>
       <c r="K83" s="2">
         <v>1.0</v>
@@ -6214,25 +6214,25 @@
         <v>0.0</v>
       </c>
       <c r="N83" s="2">
-        <v>1036.0</v>
+        <v>1042.0</v>
       </c>
       <c r="O83" s="2">
-        <v>568.0</v>
+        <v>569.0</v>
       </c>
       <c r="P83" s="2">
         <v>452.0</v>
       </c>
       <c r="Q83" s="2">
-        <v>16.0</v>
+        <v>21.0</v>
       </c>
       <c r="R83" s="2">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="S83" s="2">
         <v>21.0</v>
       </c>
       <c r="T83" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="U83" s="2">
         <v>0.0</v>
@@ -6241,7 +6241,7 @@
         <v>0.0</v>
       </c>
       <c r="W83" s="2">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
@@ -6557,7 +6557,7 @@
         <v>883.0</v>
       </c>
       <c r="J88" s="2">
-        <v>787.0</v>
+        <v>800.0</v>
       </c>
       <c r="K88" s="2">
         <v>1.0</v>
@@ -6569,13 +6569,13 @@
         <v>0.0</v>
       </c>
       <c r="N88" s="2">
-        <v>787.0</v>
+        <v>800.0</v>
       </c>
       <c r="O88" s="2">
-        <v>399.0</v>
+        <v>403.0</v>
       </c>
       <c r="P88" s="2">
-        <v>388.0</v>
+        <v>397.0</v>
       </c>
       <c r="Q88" s="2">
         <v>0.0</v>
@@ -6587,16 +6587,16 @@
         <v>27.0</v>
       </c>
       <c r="T88" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="U88" s="2">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="V88" s="2">
         <v>1.0</v>
       </c>
       <c r="W88" s="2">
-        <v>76.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
@@ -6785,13 +6785,13 @@
         <v>727.0</v>
       </c>
       <c r="O91" s="2">
-        <v>187.0</v>
+        <v>206.0</v>
       </c>
       <c r="P91" s="2">
-        <v>339.0</v>
+        <v>341.0</v>
       </c>
       <c r="Q91" s="2">
-        <v>201.0</v>
+        <v>180.0</v>
       </c>
       <c r="R91" s="2">
         <v>44.0</v>
@@ -6841,7 +6841,7 @@
         <v>1315.0</v>
       </c>
       <c r="J92" s="2">
-        <v>1071.0</v>
+        <v>1103.0</v>
       </c>
       <c r="K92" s="2">
         <v>1.0</v>
@@ -6853,13 +6853,13 @@
         <v>0.0</v>
       </c>
       <c r="N92" s="2">
-        <v>1071.0</v>
+        <v>1103.0</v>
       </c>
       <c r="O92" s="2">
-        <v>567.0</v>
+        <v>585.0</v>
       </c>
       <c r="P92" s="2">
-        <v>390.0</v>
+        <v>404.0</v>
       </c>
       <c r="Q92" s="2">
         <v>114.0</v>
@@ -6874,13 +6874,13 @@
         <v>19.0</v>
       </c>
       <c r="U92" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="V92" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="W92" s="2">
-        <v>210.0</v>
+        <v>213.0</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
@@ -6983,7 +6983,7 @@
         <v>833.0</v>
       </c>
       <c r="J94" s="2">
-        <v>766.0</v>
+        <v>769.0</v>
       </c>
       <c r="K94" s="2">
         <v>1.0</v>
@@ -6995,13 +6995,13 @@
         <v>0.0</v>
       </c>
       <c r="N94" s="2">
-        <v>766.0</v>
+        <v>769.0</v>
       </c>
       <c r="O94" s="2">
-        <v>387.0</v>
+        <v>389.0</v>
       </c>
       <c r="P94" s="2">
-        <v>376.0</v>
+        <v>377.0</v>
       </c>
       <c r="Q94" s="2">
         <v>3.0</v>
@@ -7125,7 +7125,7 @@
         <v>1426.0</v>
       </c>
       <c r="J96" s="2">
-        <v>1316.0</v>
+        <v>1325.0</v>
       </c>
       <c r="K96" s="2">
         <v>1.0</v>
@@ -7137,22 +7137,22 @@
         <v>0.0</v>
       </c>
       <c r="N96" s="2">
-        <v>1316.0</v>
+        <v>1325.0</v>
       </c>
       <c r="O96" s="2">
-        <v>786.0</v>
+        <v>792.0</v>
       </c>
       <c r="P96" s="2">
-        <v>513.0</v>
+        <v>516.0</v>
       </c>
       <c r="Q96" s="2">
         <v>17.0</v>
       </c>
       <c r="R96" s="2">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="S96" s="2">
-        <v>30.0</v>
+        <v>36.0</v>
       </c>
       <c r="T96" s="2">
         <v>0.0</v>
@@ -7164,7 +7164,7 @@
         <v>0.0</v>
       </c>
       <c r="W96" s="2">
-        <v>85.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
@@ -7267,7 +7267,7 @@
         <v>1461.0</v>
       </c>
       <c r="J98" s="2">
-        <v>1358.0</v>
+        <v>1366.0</v>
       </c>
       <c r="K98" s="2">
         <v>1.0</v>
@@ -7279,34 +7279,34 @@
         <v>0.0</v>
       </c>
       <c r="N98" s="2">
-        <v>1358.0</v>
+        <v>1366.0</v>
       </c>
       <c r="O98" s="2">
-        <v>725.0</v>
+        <v>731.0</v>
       </c>
       <c r="P98" s="2">
         <v>623.0</v>
       </c>
       <c r="Q98" s="2">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="R98" s="2">
-        <v>15.0</v>
+        <v>27.0</v>
       </c>
       <c r="S98" s="2">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
       <c r="T98" s="2">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="U98" s="2">
         <v>0.0</v>
       </c>
       <c r="V98" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="W98" s="2">
-        <v>37.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
@@ -7338,7 +7338,7 @@
         <v>880.0</v>
       </c>
       <c r="J99" s="2">
-        <v>810.0</v>
+        <v>811.0</v>
       </c>
       <c r="K99" s="2">
         <v>1.0</v>
@@ -7350,7 +7350,7 @@
         <v>0.0</v>
       </c>
       <c r="N99" s="2">
-        <v>810.0</v>
+        <v>811.0</v>
       </c>
       <c r="O99" s="2">
         <v>416.0</v>
@@ -7359,7 +7359,7 @@
         <v>392.0</v>
       </c>
       <c r="Q99" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="R99" s="2">
         <v>39.0</v>
@@ -7510,7 +7510,7 @@
         <v>59.0</v>
       </c>
       <c r="T101" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="U101" s="2">
         <v>10.0</v>
@@ -7519,7 +7519,7 @@
         <v>0.0</v>
       </c>
       <c r="W101" s="2">
-        <v>117.0</v>
+        <v>118.0</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
@@ -7551,7 +7551,7 @@
         <v>1159.0</v>
       </c>
       <c r="J102" s="2">
-        <v>1031.0</v>
+        <v>1034.0</v>
       </c>
       <c r="K102" s="2">
         <v>1.0</v>
@@ -7563,10 +7563,10 @@
         <v>0.0</v>
       </c>
       <c r="N102" s="2">
-        <v>1031.0</v>
+        <v>1034.0</v>
       </c>
       <c r="O102" s="2">
-        <v>548.0</v>
+        <v>551.0</v>
       </c>
       <c r="P102" s="2">
         <v>483.0</v>
@@ -7906,7 +7906,7 @@
         <v>1053.0</v>
       </c>
       <c r="J107" s="2">
-        <v>927.0</v>
+        <v>950.0</v>
       </c>
       <c r="K107" s="2">
         <v>1.0</v>
@@ -7918,22 +7918,22 @@
         <v>0.0</v>
       </c>
       <c r="N107" s="2">
-        <v>927.0</v>
+        <v>950.0</v>
       </c>
       <c r="O107" s="2">
-        <v>489.0</v>
+        <v>499.0</v>
       </c>
       <c r="P107" s="2">
-        <v>438.0</v>
+        <v>451.0</v>
       </c>
       <c r="Q107" s="2">
         <v>0.0</v>
       </c>
       <c r="R107" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="S107" s="2">
-        <v>73.0</v>
+        <v>81.0</v>
       </c>
       <c r="T107" s="2">
         <v>0.0</v>
@@ -7945,7 +7945,7 @@
         <v>0.0</v>
       </c>
       <c r="W107" s="2">
-        <v>84.0</v>
+        <v>93.0</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
@@ -7977,7 +7977,7 @@
         <v>950.0</v>
       </c>
       <c r="J108" s="2">
-        <v>867.0</v>
+        <v>895.0</v>
       </c>
       <c r="K108" s="2">
         <v>1.0</v>
@@ -7989,22 +7989,22 @@
         <v>0.0</v>
       </c>
       <c r="N108" s="2">
-        <v>867.0</v>
+        <v>895.0</v>
       </c>
       <c r="O108" s="2">
-        <v>549.0</v>
+        <v>563.0</v>
       </c>
       <c r="P108" s="2">
-        <v>318.0</v>
+        <v>332.0</v>
       </c>
       <c r="Q108" s="2">
         <v>0.0</v>
       </c>
       <c r="R108" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="S108" s="2">
-        <v>34.0</v>
+        <v>38.0</v>
       </c>
       <c r="T108" s="2">
         <v>0.0</v>
@@ -8016,7 +8016,7 @@
         <v>0.0</v>
       </c>
       <c r="W108" s="2">
-        <v>47.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
@@ -8332,7 +8332,7 @@
         <v>921.0</v>
       </c>
       <c r="J113" s="2">
-        <v>905.0</v>
+        <v>911.0</v>
       </c>
       <c r="K113" s="2">
         <v>1.0</v>
@@ -8344,22 +8344,22 @@
         <v>0.0</v>
       </c>
       <c r="N113" s="2">
-        <v>905.0</v>
+        <v>911.0</v>
       </c>
       <c r="O113" s="2">
         <v>458.0</v>
       </c>
       <c r="P113" s="2">
-        <v>447.0</v>
+        <v>448.0</v>
       </c>
       <c r="Q113" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="R113" s="2">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="S113" s="2">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="T113" s="2">
         <v>0.0</v>
@@ -8371,7 +8371,7 @@
         <v>0.0</v>
       </c>
       <c r="W113" s="2">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
@@ -8403,7 +8403,7 @@
         <v>924.0</v>
       </c>
       <c r="J114" s="2">
-        <v>845.0</v>
+        <v>863.0</v>
       </c>
       <c r="K114" s="2">
         <v>1.0</v>
@@ -8415,22 +8415,22 @@
         <v>0.0</v>
       </c>
       <c r="N114" s="2">
-        <v>845.0</v>
+        <v>863.0</v>
       </c>
       <c r="O114" s="2">
-        <v>511.0</v>
+        <v>522.0</v>
       </c>
       <c r="P114" s="2">
-        <v>333.0</v>
+        <v>340.0</v>
       </c>
       <c r="Q114" s="2">
         <v>1.0</v>
       </c>
       <c r="R114" s="2">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="S114" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="T114" s="2">
         <v>0.0</v>
@@ -8442,7 +8442,7 @@
         <v>0.0</v>
       </c>
       <c r="W114" s="2">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
@@ -8507,13 +8507,13 @@
         <v>1.0</v>
       </c>
       <c r="U115" s="2">
-        <v>104.0</v>
+        <v>112.0</v>
       </c>
       <c r="V115" s="2">
         <v>0.0</v>
       </c>
       <c r="W115" s="2">
-        <v>270.0</v>
+        <v>278.0</v>
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
@@ -8616,7 +8616,7 @@
         <v>1078.0</v>
       </c>
       <c r="J117" s="2">
-        <v>890.0</v>
+        <v>923.0</v>
       </c>
       <c r="K117" s="2">
         <v>1.0</v>
@@ -8628,13 +8628,13 @@
         <v>1.0</v>
       </c>
       <c r="N117" s="2">
-        <v>889.0</v>
+        <v>922.0</v>
       </c>
       <c r="O117" s="2">
-        <v>442.0</v>
+        <v>455.0</v>
       </c>
       <c r="P117" s="2">
-        <v>430.0</v>
+        <v>450.0</v>
       </c>
       <c r="Q117" s="2">
         <v>18.0</v>
@@ -8643,19 +8643,19 @@
         <v>27.0</v>
       </c>
       <c r="S117" s="2">
-        <v>65.0</v>
+        <v>82.0</v>
       </c>
       <c r="T117" s="2">
         <v>0.0</v>
       </c>
       <c r="U117" s="2">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="V117" s="2">
         <v>0.0</v>
       </c>
       <c r="W117" s="2">
-        <v>97.0</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
@@ -8687,7 +8687,7 @@
         <v>1422.0</v>
       </c>
       <c r="J118" s="2">
-        <v>1081.0</v>
+        <v>1136.0</v>
       </c>
       <c r="K118" s="2">
         <v>1.0</v>
@@ -8699,34 +8699,34 @@
         <v>0.0</v>
       </c>
       <c r="N118" s="2">
-        <v>1081.0</v>
+        <v>1136.0</v>
       </c>
       <c r="O118" s="2">
-        <v>620.0</v>
+        <v>642.0</v>
       </c>
       <c r="P118" s="2">
-        <v>455.0</v>
+        <v>488.0</v>
       </c>
       <c r="Q118" s="2">
         <v>6.0</v>
       </c>
       <c r="R118" s="2">
-        <v>58.0</v>
+        <v>61.0</v>
       </c>
       <c r="S118" s="2">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="T118" s="2">
         <v>11.0</v>
       </c>
       <c r="U118" s="2">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
       <c r="V118" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="W118" s="2">
-        <v>122.0</v>
+        <v>131.0</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
@@ -8758,7 +8758,7 @@
         <v>1084.0</v>
       </c>
       <c r="J119" s="2">
-        <v>959.0</v>
+        <v>980.0</v>
       </c>
       <c r="K119" s="2">
         <v>1.0</v>
@@ -8770,19 +8770,19 @@
         <v>0.0</v>
       </c>
       <c r="N119" s="2">
-        <v>959.0</v>
+        <v>980.0</v>
       </c>
       <c r="O119" s="2">
-        <v>554.0</v>
+        <v>565.0</v>
       </c>
       <c r="P119" s="2">
-        <v>387.0</v>
+        <v>393.0</v>
       </c>
       <c r="Q119" s="2">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
       <c r="R119" s="2">
-        <v>69.0</v>
+        <v>72.0</v>
       </c>
       <c r="S119" s="2">
         <v>20.0</v>
@@ -8797,7 +8797,7 @@
         <v>0.0</v>
       </c>
       <c r="W119" s="2">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
@@ -8829,7 +8829,7 @@
         <v>971.0</v>
       </c>
       <c r="J120" s="2">
-        <v>800.0</v>
+        <v>866.0</v>
       </c>
       <c r="K120" s="2">
         <v>1.0</v>
@@ -8841,25 +8841,25 @@
         <v>0.0</v>
       </c>
       <c r="N120" s="2">
-        <v>800.0</v>
+        <v>866.0</v>
       </c>
       <c r="O120" s="2">
-        <v>454.0</v>
+        <v>478.0</v>
       </c>
       <c r="P120" s="2">
-        <v>341.0</v>
+        <v>354.0</v>
       </c>
       <c r="Q120" s="2">
-        <v>5.0</v>
+        <v>34.0</v>
       </c>
       <c r="R120" s="2">
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
       <c r="S120" s="2">
         <v>6.0</v>
       </c>
       <c r="T120" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="U120" s="2">
         <v>3.0</v>
@@ -8868,7 +8868,7 @@
         <v>0.0</v>
       </c>
       <c r="W120" s="2">
-        <v>49.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
@@ -8900,7 +8900,7 @@
         <v>1425.0</v>
       </c>
       <c r="J121" s="2">
-        <v>1186.0</v>
+        <v>1258.0</v>
       </c>
       <c r="K121" s="2">
         <v>1.0</v>
@@ -8912,19 +8912,19 @@
         <v>0.0</v>
       </c>
       <c r="N121" s="2">
-        <v>1186.0</v>
+        <v>1258.0</v>
       </c>
       <c r="O121" s="2">
-        <v>758.0</v>
+        <v>802.0</v>
       </c>
       <c r="P121" s="2">
-        <v>413.0</v>
+        <v>434.0</v>
       </c>
       <c r="Q121" s="2">
-        <v>15.0</v>
+        <v>22.0</v>
       </c>
       <c r="R121" s="2">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="S121" s="2">
         <v>9.0</v>
@@ -8939,7 +8939,7 @@
         <v>0.0</v>
       </c>
       <c r="W121" s="2">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
@@ -8971,7 +8971,7 @@
         <v>939.0</v>
       </c>
       <c r="J122" s="2">
-        <v>759.0</v>
+        <v>778.0</v>
       </c>
       <c r="K122" s="2">
         <v>1.0</v>
@@ -8983,13 +8983,13 @@
         <v>4.0</v>
       </c>
       <c r="N122" s="2">
-        <v>755.0</v>
+        <v>774.0</v>
       </c>
       <c r="O122" s="2">
-        <v>418.0</v>
+        <v>428.0</v>
       </c>
       <c r="P122" s="2">
-        <v>326.0</v>
+        <v>335.0</v>
       </c>
       <c r="Q122" s="2">
         <v>15.0</v>
@@ -8998,19 +8998,19 @@
         <v>32.0</v>
       </c>
       <c r="S122" s="2">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
       <c r="T122" s="2">
         <v>0.0</v>
       </c>
       <c r="U122" s="2">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="V122" s="2">
         <v>2.0</v>
       </c>
       <c r="W122" s="2">
-        <v>66.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
@@ -9610,7 +9610,7 @@
         <v>865.0</v>
       </c>
       <c r="J131" s="2">
-        <v>758.0</v>
+        <v>786.0</v>
       </c>
       <c r="K131" s="2">
         <v>1.0</v>
@@ -9622,25 +9622,25 @@
         <v>0.0</v>
       </c>
       <c r="N131" s="2">
-        <v>758.0</v>
+        <v>786.0</v>
       </c>
       <c r="O131" s="2">
-        <v>393.0</v>
+        <v>405.0</v>
       </c>
       <c r="P131" s="2">
-        <v>345.0</v>
+        <v>347.0</v>
       </c>
       <c r="Q131" s="2">
+        <v>34.0</v>
+      </c>
+      <c r="R131" s="2">
+        <v>37.0</v>
+      </c>
+      <c r="S131" s="2">
         <v>20.0</v>
       </c>
-      <c r="R131" s="2">
-        <v>34.0</v>
-      </c>
-      <c r="S131" s="2">
-        <v>15.0</v>
-      </c>
       <c r="T131" s="2">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
       <c r="U131" s="2">
         <v>5.0</v>
@@ -9649,7 +9649,7 @@
         <v>0.0</v>
       </c>
       <c r="W131" s="2">
-        <v>65.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="132" ht="15.75" customHeight="1">
@@ -9681,7 +9681,7 @@
         <v>1427.0</v>
       </c>
       <c r="J132" s="2">
-        <v>1354.0</v>
+        <v>1359.0</v>
       </c>
       <c r="K132" s="2">
         <v>1.0</v>
@@ -9693,19 +9693,19 @@
         <v>0.0</v>
       </c>
       <c r="N132" s="2">
-        <v>1354.0</v>
+        <v>1359.0</v>
       </c>
       <c r="O132" s="2">
-        <v>767.0</v>
+        <v>768.0</v>
       </c>
       <c r="P132" s="2">
-        <v>563.0</v>
+        <v>567.0</v>
       </c>
       <c r="Q132" s="2">
         <v>24.0</v>
       </c>
       <c r="R132" s="2">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
       <c r="S132" s="2">
         <v>3.0</v>
@@ -9720,7 +9720,7 @@
         <v>0.0</v>
       </c>
       <c r="W132" s="2">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
@@ -10036,7 +10036,7 @@
         <v>1211.0</v>
       </c>
       <c r="J137" s="2">
-        <v>1000.0</v>
+        <v>1001.0</v>
       </c>
       <c r="K137" s="2">
         <v>1.0</v>
@@ -10048,13 +10048,13 @@
         <v>0.0</v>
       </c>
       <c r="N137" s="2">
-        <v>1000.0</v>
+        <v>1001.0</v>
       </c>
       <c r="O137" s="2">
         <v>543.0</v>
       </c>
       <c r="P137" s="2">
-        <v>426.0</v>
+        <v>427.0</v>
       </c>
       <c r="Q137" s="2">
         <v>31.0</v>
@@ -10249,7 +10249,7 @@
         <v>1236.0</v>
       </c>
       <c r="J140" s="2">
-        <v>1086.0</v>
+        <v>1106.0</v>
       </c>
       <c r="K140" s="2">
         <v>1.0</v>
@@ -10261,25 +10261,25 @@
         <v>0.0</v>
       </c>
       <c r="N140" s="2">
-        <v>1086.0</v>
+        <v>1106.0</v>
       </c>
       <c r="O140" s="2">
-        <v>584.0</v>
+        <v>595.0</v>
       </c>
       <c r="P140" s="2">
-        <v>480.0</v>
+        <v>487.0</v>
       </c>
       <c r="Q140" s="2">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
       <c r="R140" s="2">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
       <c r="S140" s="2">
-        <v>83.0</v>
+        <v>89.0</v>
       </c>
       <c r="T140" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="U140" s="2">
         <v>6.0</v>
@@ -10288,7 +10288,7 @@
         <v>0.0</v>
       </c>
       <c r="W140" s="2">
-        <v>104.0</v>
+        <v>115.0</v>
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
@@ -10320,7 +10320,7 @@
         <v>1244.0</v>
       </c>
       <c r="J141" s="2">
-        <v>1087.0</v>
+        <v>1113.0</v>
       </c>
       <c r="K141" s="2">
         <v>1.0</v>
@@ -10332,22 +10332,22 @@
         <v>1.0</v>
       </c>
       <c r="N141" s="2">
-        <v>1086.0</v>
+        <v>1112.0</v>
       </c>
       <c r="O141" s="2">
-        <v>678.0</v>
+        <v>689.0</v>
       </c>
       <c r="P141" s="2">
-        <v>394.0</v>
+        <v>408.0</v>
       </c>
       <c r="Q141" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="R141" s="2">
         <v>24.0</v>
       </c>
       <c r="S141" s="2">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
       <c r="T141" s="2">
         <v>2.0</v>
@@ -10356,10 +10356,10 @@
         <v>7.0</v>
       </c>
       <c r="V141" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="W141" s="2">
-        <v>36.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1">
@@ -10462,7 +10462,7 @@
         <v>1469.0</v>
       </c>
       <c r="J143" s="2">
-        <v>1116.0</v>
+        <v>1192.0</v>
       </c>
       <c r="K143" s="2">
         <v>1.0</v>
@@ -10474,19 +10474,19 @@
         <v>1.0</v>
       </c>
       <c r="N143" s="2">
-        <v>1115.0</v>
+        <v>1191.0</v>
       </c>
       <c r="O143" s="2">
-        <v>648.0</v>
+        <v>692.0</v>
       </c>
       <c r="P143" s="2">
-        <v>467.0</v>
+        <v>499.0</v>
       </c>
       <c r="Q143" s="2">
         <v>1.0</v>
       </c>
       <c r="R143" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S143" s="2">
         <v>0.0</v>
@@ -10501,7 +10501,7 @@
         <v>0.0</v>
       </c>
       <c r="W143" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1">
@@ -10533,7 +10533,7 @@
         <v>1487.0</v>
       </c>
       <c r="J144" s="2">
-        <v>1212.0</v>
+        <v>1313.0</v>
       </c>
       <c r="K144" s="2">
         <v>1.0</v>
@@ -10545,13 +10545,13 @@
         <v>0.0</v>
       </c>
       <c r="N144" s="2">
-        <v>1212.0</v>
+        <v>1313.0</v>
       </c>
       <c r="O144" s="2">
-        <v>680.0</v>
+        <v>738.0</v>
       </c>
       <c r="P144" s="2">
-        <v>532.0</v>
+        <v>575.0</v>
       </c>
       <c r="Q144" s="2">
         <v>0.0</v>
@@ -10604,7 +10604,7 @@
         <v>1012.0</v>
       </c>
       <c r="J145" s="2">
-        <v>940.0</v>
+        <v>942.0</v>
       </c>
       <c r="K145" s="2">
         <v>1.0</v>
@@ -10616,13 +10616,13 @@
         <v>0.0</v>
       </c>
       <c r="N145" s="2">
-        <v>940.0</v>
+        <v>942.0</v>
       </c>
       <c r="O145" s="2">
         <v>418.0</v>
       </c>
       <c r="P145" s="2">
-        <v>482.0</v>
+        <v>484.0</v>
       </c>
       <c r="Q145" s="2">
         <v>40.0</v>
@@ -10634,7 +10634,7 @@
         <v>23.0</v>
       </c>
       <c r="T145" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U145" s="2">
         <v>16.0</v>
@@ -10643,7 +10643,7 @@
         <v>1.0</v>
       </c>
       <c r="W145" s="2">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="146" ht="15.75" customHeight="1">
@@ -10675,7 +10675,7 @@
         <v>863.0</v>
       </c>
       <c r="J146" s="2">
-        <v>621.0</v>
+        <v>683.0</v>
       </c>
       <c r="K146" s="2">
         <v>1.0</v>
@@ -10687,13 +10687,13 @@
         <v>0.0</v>
       </c>
       <c r="N146" s="2">
-        <v>621.0</v>
+        <v>683.0</v>
       </c>
       <c r="O146" s="2">
-        <v>266.0</v>
+        <v>318.0</v>
       </c>
       <c r="P146" s="2">
-        <v>355.0</v>
+        <v>365.0</v>
       </c>
       <c r="Q146" s="2">
         <v>0.0</v>
@@ -10746,7 +10746,7 @@
         <v>1424.0</v>
       </c>
       <c r="J147" s="2">
-        <v>746.0</v>
+        <v>748.0</v>
       </c>
       <c r="K147" s="2">
         <v>1.0</v>
@@ -10758,13 +10758,13 @@
         <v>0.0</v>
       </c>
       <c r="N147" s="2">
-        <v>746.0</v>
+        <v>748.0</v>
       </c>
       <c r="O147" s="2">
-        <v>383.0</v>
+        <v>384.0</v>
       </c>
       <c r="P147" s="2">
-        <v>359.0</v>
+        <v>360.0</v>
       </c>
       <c r="Q147" s="2">
         <v>4.0</v>
@@ -10817,7 +10817,7 @@
         <v>1269.0</v>
       </c>
       <c r="J148" s="2">
-        <v>990.0</v>
+        <v>1100.0</v>
       </c>
       <c r="K148" s="2">
         <v>1.0</v>
@@ -10829,34 +10829,34 @@
         <v>0.0</v>
       </c>
       <c r="N148" s="2">
-        <v>990.0</v>
+        <v>1100.0</v>
       </c>
       <c r="O148" s="2">
-        <v>498.0</v>
+        <v>572.0</v>
       </c>
       <c r="P148" s="2">
-        <v>492.0</v>
+        <v>519.0</v>
       </c>
       <c r="Q148" s="2">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="R148" s="2">
         <v>22.0</v>
       </c>
       <c r="S148" s="2">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="T148" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="U148" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="V148" s="2">
         <v>0.0</v>
       </c>
       <c r="W148" s="2">
-        <v>26.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1">
@@ -10888,7 +10888,7 @@
         <v>1218.0</v>
       </c>
       <c r="J149" s="2">
-        <v>788.0</v>
+        <v>880.0</v>
       </c>
       <c r="K149" s="2">
         <v>1.0</v>
@@ -10900,16 +10900,16 @@
         <v>0.0</v>
       </c>
       <c r="N149" s="2">
-        <v>788.0</v>
+        <v>880.0</v>
       </c>
       <c r="O149" s="2">
-        <v>474.0</v>
+        <v>530.0</v>
       </c>
       <c r="P149" s="2">
-        <v>308.0</v>
+        <v>342.0</v>
       </c>
       <c r="Q149" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="R149" s="2">
         <v>27.0</v>
@@ -11030,7 +11030,7 @@
         <v>695.0</v>
       </c>
       <c r="J151" s="2">
-        <v>587.0</v>
+        <v>637.0</v>
       </c>
       <c r="K151" s="2">
         <v>1.0</v>
@@ -11042,22 +11042,22 @@
         <v>0.0</v>
       </c>
       <c r="N151" s="2">
-        <v>587.0</v>
+        <v>637.0</v>
       </c>
       <c r="O151" s="2">
-        <v>303.0</v>
+        <v>334.0</v>
       </c>
       <c r="P151" s="2">
-        <v>284.0</v>
+        <v>302.0</v>
       </c>
       <c r="Q151" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R151" s="2">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="S151" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T151" s="2">
         <v>0.0</v>
@@ -11069,7 +11069,7 @@
         <v>0.0</v>
       </c>
       <c r="W151" s="2">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1">
@@ -11101,7 +11101,7 @@
         <v>942.0</v>
       </c>
       <c r="J152" s="2">
-        <v>827.0</v>
+        <v>850.0</v>
       </c>
       <c r="K152" s="2">
         <v>1.0</v>
@@ -11113,19 +11113,19 @@
         <v>1.0</v>
       </c>
       <c r="N152" s="2">
-        <v>826.0</v>
+        <v>849.0</v>
       </c>
       <c r="O152" s="2">
-        <v>418.0</v>
+        <v>426.0</v>
       </c>
       <c r="P152" s="2">
-        <v>409.0</v>
+        <v>420.0</v>
       </c>
       <c r="Q152" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="R152" s="2">
-        <v>76.0</v>
+        <v>80.0</v>
       </c>
       <c r="S152" s="2">
         <v>1.0</v>
@@ -11140,7 +11140,7 @@
         <v>0.0</v>
       </c>
       <c r="W152" s="2">
-        <v>77.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="153" ht="15.75" customHeight="1">
@@ -11172,7 +11172,7 @@
         <v>1018.0</v>
       </c>
       <c r="J153" s="2">
-        <v>855.0</v>
+        <v>863.0</v>
       </c>
       <c r="K153" s="2">
         <v>1.0</v>
@@ -11184,34 +11184,34 @@
         <v>0.0</v>
       </c>
       <c r="N153" s="2">
-        <v>855.0</v>
+        <v>863.0</v>
       </c>
       <c r="O153" s="2">
-        <v>416.0</v>
+        <v>422.0</v>
       </c>
       <c r="P153" s="2">
-        <v>438.0</v>
+        <v>440.0</v>
       </c>
       <c r="Q153" s="2">
         <v>1.0</v>
       </c>
       <c r="R153" s="2">
-        <v>40.0</v>
+        <v>43.0</v>
       </c>
       <c r="S153" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="T153" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="U153" s="2">
         <v>0.0</v>
       </c>
       <c r="V153" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="W153" s="2">
-        <v>47.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="154" ht="15.75" customHeight="1">
@@ -11243,7 +11243,7 @@
         <v>999.0</v>
       </c>
       <c r="J154" s="2">
-        <v>802.0</v>
+        <v>847.0</v>
       </c>
       <c r="K154" s="2">
         <v>1.0</v>
@@ -11255,34 +11255,34 @@
         <v>0.0</v>
       </c>
       <c r="N154" s="2">
-        <v>802.0</v>
+        <v>847.0</v>
       </c>
       <c r="O154" s="2">
-        <v>216.0</v>
+        <v>255.0</v>
       </c>
       <c r="P154" s="2">
-        <v>353.0</v>
+        <v>359.0</v>
       </c>
       <c r="Q154" s="2">
         <v>233.0</v>
       </c>
       <c r="R154" s="2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="S154" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="T154" s="2">
         <v>0.0</v>
       </c>
       <c r="U154" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V154" s="2">
         <v>0.0</v>
       </c>
       <c r="W154" s="2">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="155" ht="15.75" customHeight="1">
@@ -11385,7 +11385,7 @@
         <v>1119.0</v>
       </c>
       <c r="J156" s="2">
-        <v>943.0</v>
+        <v>974.0</v>
       </c>
       <c r="K156" s="2">
         <v>1.0</v>
@@ -11397,22 +11397,22 @@
         <v>0.0</v>
       </c>
       <c r="N156" s="2">
-        <v>943.0</v>
+        <v>974.0</v>
       </c>
       <c r="O156" s="2">
-        <v>452.0</v>
+        <v>482.0</v>
       </c>
       <c r="P156" s="2">
-        <v>490.0</v>
+        <v>491.0</v>
       </c>
       <c r="Q156" s="2">
         <v>1.0</v>
       </c>
       <c r="R156" s="2">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="S156" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T156" s="2">
         <v>0.0</v>
@@ -11424,7 +11424,7 @@
         <v>0.0</v>
       </c>
       <c r="W156" s="2">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="157" ht="15.75" customHeight="1">
@@ -11527,7 +11527,7 @@
         <v>1353.0</v>
       </c>
       <c r="J158" s="2">
-        <v>1064.0</v>
+        <v>1118.0</v>
       </c>
       <c r="K158" s="2">
         <v>1.0</v>
@@ -11539,25 +11539,25 @@
         <v>0.0</v>
       </c>
       <c r="N158" s="2">
-        <v>1064.0</v>
+        <v>1118.0</v>
       </c>
       <c r="O158" s="2">
-        <v>501.0</v>
+        <v>524.0</v>
       </c>
       <c r="P158" s="2">
-        <v>563.0</v>
+        <v>594.0</v>
       </c>
       <c r="Q158" s="2">
         <v>0.0</v>
       </c>
       <c r="R158" s="2">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="S158" s="2">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
       <c r="T158" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="U158" s="2">
         <v>0.0</v>
@@ -11566,7 +11566,7 @@
         <v>0.0</v>
       </c>
       <c r="W158" s="2">
-        <v>72.0</v>
+        <v>77.0</v>
       </c>
     </row>
     <row r="159" ht="15.75" customHeight="1">
@@ -11598,7 +11598,7 @@
         <v>1153.0</v>
       </c>
       <c r="J159" s="2">
-        <v>1019.0</v>
+        <v>1054.0</v>
       </c>
       <c r="K159" s="2">
         <v>1.0</v>
@@ -11610,34 +11610,34 @@
         <v>1.0</v>
       </c>
       <c r="N159" s="2">
-        <v>1018.0</v>
+        <v>1053.0</v>
       </c>
       <c r="O159" s="2">
-        <v>602.0</v>
+        <v>618.0</v>
       </c>
       <c r="P159" s="2">
-        <v>417.0</v>
+        <v>436.0</v>
       </c>
       <c r="Q159" s="2">
         <v>0.0</v>
       </c>
       <c r="R159" s="2">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="S159" s="2">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="T159" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="U159" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="V159" s="2">
         <v>0.0</v>
       </c>
       <c r="W159" s="2">
-        <v>44.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="160" ht="15.75" customHeight="1">
@@ -11669,7 +11669,7 @@
         <v>1283.0</v>
       </c>
       <c r="J160" s="2">
-        <v>1175.0</v>
+        <v>1206.0</v>
       </c>
       <c r="K160" s="2">
         <v>1.0</v>
@@ -11681,13 +11681,13 @@
         <v>0.0</v>
       </c>
       <c r="N160" s="2">
-        <v>1175.0</v>
+        <v>1206.0</v>
       </c>
       <c r="O160" s="2">
-        <v>605.0</v>
+        <v>613.0</v>
       </c>
       <c r="P160" s="2">
-        <v>570.0</v>
+        <v>593.0</v>
       </c>
       <c r="Q160" s="2">
         <v>0.0</v>
@@ -11740,7 +11740,7 @@
         <v>1401.0</v>
       </c>
       <c r="J161" s="2">
-        <v>1109.0</v>
+        <v>1132.0</v>
       </c>
       <c r="K161" s="2">
         <v>1.0</v>
@@ -11752,16 +11752,16 @@
         <v>0.0</v>
       </c>
       <c r="N161" s="2">
-        <v>1109.0</v>
+        <v>1132.0</v>
       </c>
       <c r="O161" s="2">
-        <v>602.0</v>
+        <v>614.0</v>
       </c>
       <c r="P161" s="2">
-        <v>499.0</v>
+        <v>500.0</v>
       </c>
       <c r="Q161" s="2">
-        <v>8.0</v>
+        <v>18.0</v>
       </c>
       <c r="R161" s="2">
         <v>21.0</v>
@@ -11773,13 +11773,13 @@
         <v>0.0</v>
       </c>
       <c r="U161" s="2">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="V161" s="2">
         <v>0.0</v>
       </c>
       <c r="W161" s="2">
-        <v>32.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="162" ht="15.75" customHeight="1">
@@ -11811,7 +11811,7 @@
         <v>1184.0</v>
       </c>
       <c r="J162" s="2">
-        <v>1013.0</v>
+        <v>1099.0</v>
       </c>
       <c r="K162" s="2">
         <v>1.0</v>
@@ -11823,22 +11823,22 @@
         <v>1.0</v>
       </c>
       <c r="N162" s="2">
-        <v>1012.0</v>
+        <v>1098.0</v>
       </c>
       <c r="O162" s="2">
-        <v>64.0</v>
+        <v>100.0</v>
       </c>
       <c r="P162" s="2">
-        <v>228.0</v>
+        <v>260.0</v>
       </c>
       <c r="Q162" s="2">
-        <v>721.0</v>
+        <v>739.0</v>
       </c>
       <c r="R162" s="2">
         <v>28.0</v>
       </c>
       <c r="S162" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T162" s="2">
         <v>0.0</v>
@@ -11850,7 +11850,7 @@
         <v>1.0</v>
       </c>
       <c r="W162" s="2">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="163" ht="15.75" customHeight="1">
@@ -11882,7 +11882,7 @@
         <v>1298.0</v>
       </c>
       <c r="J163" s="2">
-        <v>805.0</v>
+        <v>948.0</v>
       </c>
       <c r="K163" s="2">
         <v>1.0</v>
@@ -11894,34 +11894,34 @@
         <v>0.0</v>
       </c>
       <c r="N163" s="2">
-        <v>805.0</v>
+        <v>948.0</v>
       </c>
       <c r="O163" s="2">
-        <v>35.0</v>
+        <v>91.0</v>
       </c>
       <c r="P163" s="2">
-        <v>379.0</v>
+        <v>459.0</v>
       </c>
       <c r="Q163" s="2">
-        <v>391.0</v>
+        <v>398.0</v>
       </c>
       <c r="R163" s="2">
-        <v>61.0</v>
+        <v>86.0</v>
       </c>
       <c r="S163" s="2">
         <v>66.0</v>
       </c>
       <c r="T163" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="U163" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="V163" s="2">
         <v>0.0</v>
       </c>
       <c r="W163" s="2">
-        <v>131.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="164" ht="15.75" customHeight="1">
@@ -12095,7 +12095,7 @@
         <v>932.0</v>
       </c>
       <c r="J166" s="2">
-        <v>837.0</v>
+        <v>870.0</v>
       </c>
       <c r="K166" s="2">
         <v>1.0</v>
@@ -12107,25 +12107,25 @@
         <v>0.0</v>
       </c>
       <c r="N166" s="2">
-        <v>837.0</v>
+        <v>870.0</v>
       </c>
       <c r="O166" s="2">
-        <v>480.0</v>
+        <v>502.0</v>
       </c>
       <c r="P166" s="2">
-        <v>357.0</v>
+        <v>368.0</v>
       </c>
       <c r="Q166" s="2">
         <v>0.0</v>
       </c>
       <c r="R166" s="2">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="S166" s="2">
         <v>26.0</v>
       </c>
       <c r="T166" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="U166" s="2">
         <v>0.0</v>
@@ -12134,7 +12134,7 @@
         <v>0.0</v>
       </c>
       <c r="W166" s="2">
-        <v>58.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="167" ht="15.75" customHeight="1">
@@ -12237,7 +12237,7 @@
         <v>948.0</v>
       </c>
       <c r="J168" s="2">
-        <v>884.0</v>
+        <v>920.0</v>
       </c>
       <c r="K168" s="2">
         <v>1.0</v>
@@ -12249,19 +12249,19 @@
         <v>0.0</v>
       </c>
       <c r="N168" s="2">
-        <v>884.0</v>
+        <v>920.0</v>
       </c>
       <c r="O168" s="2">
-        <v>358.0</v>
+        <v>366.0</v>
       </c>
       <c r="P168" s="2">
-        <v>410.0</v>
+        <v>415.0</v>
       </c>
       <c r="Q168" s="2">
-        <v>116.0</v>
+        <v>139.0</v>
       </c>
       <c r="R168" s="2">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="S168" s="2">
         <v>0.0</v>
@@ -12276,7 +12276,7 @@
         <v>0.0</v>
       </c>
       <c r="W168" s="2">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="169" ht="15.75" customHeight="1">
@@ -12308,7 +12308,7 @@
         <v>503.0</v>
       </c>
       <c r="J169" s="2">
-        <v>470.0</v>
+        <v>471.0</v>
       </c>
       <c r="K169" s="2">
         <v>1.0</v>
@@ -12320,10 +12320,10 @@
         <v>0.0</v>
       </c>
       <c r="N169" s="2">
-        <v>470.0</v>
+        <v>471.0</v>
       </c>
       <c r="O169" s="2">
-        <v>246.0</v>
+        <v>247.0</v>
       </c>
       <c r="P169" s="2">
         <v>215.0</v>
@@ -12397,10 +12397,10 @@
         <v>142.0</v>
       </c>
       <c r="P170" s="2">
-        <v>395.0</v>
+        <v>394.0</v>
       </c>
       <c r="Q170" s="2">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
       <c r="R170" s="2">
         <v>19.0</v>
@@ -12521,7 +12521,7 @@
         <v>1079.0</v>
       </c>
       <c r="J172" s="2">
-        <v>785.0</v>
+        <v>891.0</v>
       </c>
       <c r="K172" s="2">
         <v>1.0</v>
@@ -12533,34 +12533,34 @@
         <v>0.0</v>
       </c>
       <c r="N172" s="2">
-        <v>785.0</v>
+        <v>891.0</v>
       </c>
       <c r="O172" s="2">
-        <v>422.0</v>
+        <v>507.0</v>
       </c>
       <c r="P172" s="2">
-        <v>363.0</v>
+        <v>384.0</v>
       </c>
       <c r="Q172" s="2">
         <v>0.0</v>
       </c>
       <c r="R172" s="2">
-        <v>46.0</v>
+        <v>62.0</v>
       </c>
       <c r="S172" s="2">
+        <v>58.0</v>
+      </c>
+      <c r="T172" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="U172" s="2">
         <v>17.0</v>
       </c>
-      <c r="T172" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="U172" s="2">
-        <v>9.0</v>
-      </c>
       <c r="V172" s="2">
         <v>0.0</v>
       </c>
       <c r="W172" s="2">
-        <v>73.0</v>
+        <v>151.0</v>
       </c>
     </row>
     <row r="173" ht="15.75" customHeight="1">
@@ -12690,7 +12690,7 @@
         <v>53.0</v>
       </c>
       <c r="S174" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T174" s="2">
         <v>0.0</v>
@@ -12702,7 +12702,7 @@
         <v>0.0</v>
       </c>
       <c r="W174" s="2">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="175" ht="15.75" customHeight="1">
@@ -12805,7 +12805,7 @@
         <v>1045.0</v>
       </c>
       <c r="J176" s="2">
-        <v>785.0</v>
+        <v>862.0</v>
       </c>
       <c r="K176" s="2">
         <v>1.0</v>
@@ -12817,13 +12817,13 @@
         <v>0.0</v>
       </c>
       <c r="N176" s="2">
-        <v>785.0</v>
+        <v>862.0</v>
       </c>
       <c r="O176" s="2">
-        <v>368.0</v>
+        <v>417.0</v>
       </c>
       <c r="P176" s="2">
-        <v>413.0</v>
+        <v>441.0</v>
       </c>
       <c r="Q176" s="2">
         <v>4.0</v>
@@ -12832,19 +12832,19 @@
         <v>63.0</v>
       </c>
       <c r="S176" s="2">
-        <v>23.0</v>
+        <v>28.0</v>
       </c>
       <c r="T176" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U176" s="2">
-        <v>31.0</v>
+        <v>43.0</v>
       </c>
       <c r="V176" s="2">
         <v>2.0</v>
       </c>
       <c r="W176" s="2">
-        <v>119.0</v>
+        <v>137.0</v>
       </c>
     </row>
     <row r="177" ht="15.75" customHeight="1">
@@ -12876,7 +12876,7 @@
         <v>1075.0</v>
       </c>
       <c r="J177" s="2">
-        <v>720.0</v>
+        <v>792.0</v>
       </c>
       <c r="K177" s="2">
         <v>1.0</v>
@@ -12888,34 +12888,34 @@
         <v>0.0</v>
       </c>
       <c r="N177" s="2">
-        <v>720.0</v>
+        <v>792.0</v>
       </c>
       <c r="O177" s="2">
-        <v>416.0</v>
+        <v>458.0</v>
       </c>
       <c r="P177" s="2">
-        <v>304.0</v>
+        <v>334.0</v>
       </c>
       <c r="Q177" s="2">
         <v>0.0</v>
       </c>
       <c r="R177" s="2">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="S177" s="2">
-        <v>27.0</v>
+        <v>39.0</v>
       </c>
       <c r="T177" s="2">
         <v>5.0</v>
       </c>
       <c r="U177" s="2">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
       <c r="V177" s="2">
         <v>0.0</v>
       </c>
       <c r="W177" s="2">
-        <v>84.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="178" ht="15.75" customHeight="1">
@@ -12947,7 +12947,7 @@
         <v>1008.0</v>
       </c>
       <c r="J178" s="2">
-        <v>704.0</v>
+        <v>730.0</v>
       </c>
       <c r="K178" s="2">
         <v>1.0</v>
@@ -12959,13 +12959,13 @@
         <v>0.0</v>
       </c>
       <c r="N178" s="2">
-        <v>704.0</v>
+        <v>730.0</v>
       </c>
       <c r="O178" s="2">
-        <v>349.0</v>
+        <v>363.0</v>
       </c>
       <c r="P178" s="2">
-        <v>354.0</v>
+        <v>366.0</v>
       </c>
       <c r="Q178" s="2">
         <v>1.0</v>
@@ -12974,19 +12974,19 @@
         <v>20.0</v>
       </c>
       <c r="S178" s="2">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="T178" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="U178" s="2">
-        <v>90.0</v>
+        <v>92.0</v>
       </c>
       <c r="V178" s="2">
         <v>0.0</v>
       </c>
       <c r="W178" s="2">
-        <v>122.0</v>
+        <v>127.0</v>
       </c>
     </row>
     <row r="179" ht="15.75" customHeight="1">
@@ -13018,7 +13018,7 @@
         <v>1061.0</v>
       </c>
       <c r="J179" s="2">
-        <v>894.0</v>
+        <v>916.0</v>
       </c>
       <c r="K179" s="2">
         <v>1.0</v>
@@ -13030,13 +13030,13 @@
         <v>0.0</v>
       </c>
       <c r="N179" s="2">
-        <v>894.0</v>
+        <v>916.0</v>
       </c>
       <c r="O179" s="2">
-        <v>557.0</v>
+        <v>568.0</v>
       </c>
       <c r="P179" s="2">
-        <v>336.0</v>
+        <v>347.0</v>
       </c>
       <c r="Q179" s="2">
         <v>1.0</v>
@@ -13045,7 +13045,7 @@
         <v>51.0</v>
       </c>
       <c r="S179" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="T179" s="2">
         <v>0.0</v>
@@ -13057,7 +13057,7 @@
         <v>0.0</v>
       </c>
       <c r="W179" s="2">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="180" ht="15.75" customHeight="1">
@@ -13089,7 +13089,7 @@
         <v>781.0</v>
       </c>
       <c r="J180" s="2">
-        <v>589.0</v>
+        <v>638.0</v>
       </c>
       <c r="K180" s="2">
         <v>1.0</v>
@@ -13101,22 +13101,22 @@
         <v>0.0</v>
       </c>
       <c r="N180" s="2">
-        <v>589.0</v>
+        <v>638.0</v>
       </c>
       <c r="O180" s="2">
-        <v>310.0</v>
+        <v>342.0</v>
       </c>
       <c r="P180" s="2">
-        <v>279.0</v>
+        <v>296.0</v>
       </c>
       <c r="Q180" s="2">
         <v>0.0</v>
       </c>
       <c r="R180" s="2">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="S180" s="2">
-        <v>19.0</v>
+        <v>24.0</v>
       </c>
       <c r="T180" s="2">
         <v>3.0</v>
@@ -13128,7 +13128,7 @@
         <v>0.0</v>
       </c>
       <c r="W180" s="2">
-        <v>57.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="181" ht="15.75" customHeight="1">
@@ -13160,7 +13160,7 @@
         <v>855.0</v>
       </c>
       <c r="J181" s="2">
-        <v>609.0</v>
+        <v>625.0</v>
       </c>
       <c r="K181" s="2">
         <v>1.0</v>
@@ -13172,13 +13172,13 @@
         <v>0.0</v>
       </c>
       <c r="N181" s="2">
-        <v>609.0</v>
+        <v>625.0</v>
       </c>
       <c r="O181" s="2">
-        <v>325.0</v>
+        <v>337.0</v>
       </c>
       <c r="P181" s="2">
-        <v>284.0</v>
+        <v>288.0</v>
       </c>
       <c r="Q181" s="2">
         <v>0.0</v>
@@ -13187,10 +13187,10 @@
         <v>15.0</v>
       </c>
       <c r="S181" s="2">
-        <v>39.0</v>
+        <v>45.0</v>
       </c>
       <c r="T181" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="U181" s="2">
         <v>110.0</v>
@@ -13199,7 +13199,7 @@
         <v>0.0</v>
       </c>
       <c r="W181" s="2">
-        <v>164.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="182" ht="15.75" customHeight="1">
@@ -13373,7 +13373,7 @@
         <v>899.0</v>
       </c>
       <c r="J184" s="2">
-        <v>645.0</v>
+        <v>700.0</v>
       </c>
       <c r="K184" s="2">
         <v>1.0</v>
@@ -13385,34 +13385,34 @@
         <v>1.0</v>
       </c>
       <c r="N184" s="2">
-        <v>644.0</v>
+        <v>699.0</v>
       </c>
       <c r="O184" s="2">
-        <v>318.0</v>
+        <v>348.0</v>
       </c>
       <c r="P184" s="2">
-        <v>326.0</v>
+        <v>351.0</v>
       </c>
       <c r="Q184" s="2">
         <v>1.0</v>
       </c>
       <c r="R184" s="2">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="S184" s="2">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
       <c r="T184" s="2">
         <v>4.0</v>
       </c>
       <c r="U184" s="2">
-        <v>2.0</v>
+        <v>34.0</v>
       </c>
       <c r="V184" s="2">
         <v>0.0</v>
       </c>
       <c r="W184" s="2">
-        <v>48.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="185" ht="15.75" customHeight="1">
@@ -13444,7 +13444,7 @@
         <v>1000.0</v>
       </c>
       <c r="J185" s="2">
-        <v>935.0</v>
+        <v>945.0</v>
       </c>
       <c r="K185" s="2">
         <v>1.0</v>
@@ -13456,13 +13456,13 @@
         <v>0.0</v>
       </c>
       <c r="N185" s="2">
-        <v>935.0</v>
+        <v>945.0</v>
       </c>
       <c r="O185" s="2">
-        <v>504.0</v>
+        <v>512.0</v>
       </c>
       <c r="P185" s="2">
-        <v>431.0</v>
+        <v>433.0</v>
       </c>
       <c r="Q185" s="2">
         <v>0.0</v>
@@ -13728,7 +13728,7 @@
         <v>1282.0</v>
       </c>
       <c r="J189" s="2">
-        <v>1046.0</v>
+        <v>1201.0</v>
       </c>
       <c r="K189" s="2">
         <v>1.0</v>
@@ -13740,25 +13740,25 @@
         <v>0.0</v>
       </c>
       <c r="N189" s="2">
-        <v>1046.0</v>
+        <v>1201.0</v>
       </c>
       <c r="O189" s="2">
-        <v>436.0</v>
+        <v>501.0</v>
       </c>
       <c r="P189" s="2">
-        <v>336.0</v>
+        <v>420.0</v>
       </c>
       <c r="Q189" s="2">
-        <v>274.0</v>
+        <v>280.0</v>
       </c>
       <c r="R189" s="2">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
       <c r="S189" s="2">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="T189" s="2">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="U189" s="2">
         <v>0.0</v>
@@ -13767,7 +13767,7 @@
         <v>0.0</v>
       </c>
       <c r="W189" s="2">
-        <v>45.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="190" ht="15.75" customHeight="1">
@@ -13799,7 +13799,7 @@
         <v>1393.0</v>
       </c>
       <c r="J190" s="2">
-        <v>1233.0</v>
+        <v>1256.0</v>
       </c>
       <c r="K190" s="2">
         <v>1.0</v>
@@ -13811,22 +13811,22 @@
         <v>0.0</v>
       </c>
       <c r="N190" s="2">
-        <v>1233.0</v>
+        <v>1256.0</v>
       </c>
       <c r="O190" s="2">
-        <v>727.0</v>
+        <v>743.0</v>
       </c>
       <c r="P190" s="2">
-        <v>474.0</v>
+        <v>481.0</v>
       </c>
       <c r="Q190" s="2">
         <v>32.0</v>
       </c>
       <c r="R190" s="2">
-        <v>52.0</v>
+        <v>55.0</v>
       </c>
       <c r="S190" s="2">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
       <c r="T190" s="2">
         <v>7.0</v>
@@ -13838,7 +13838,7 @@
         <v>0.0</v>
       </c>
       <c r="W190" s="2">
-        <v>126.0</v>
+        <v>131.0</v>
       </c>
     </row>
     <row r="191" ht="15.75" customHeight="1">
@@ -13870,7 +13870,7 @@
         <v>1363.0</v>
       </c>
       <c r="J191" s="2">
-        <v>1184.0</v>
+        <v>1249.0</v>
       </c>
       <c r="K191" s="2">
         <v>1.0</v>
@@ -13882,16 +13882,16 @@
         <v>0.0</v>
       </c>
       <c r="N191" s="2">
-        <v>1184.0</v>
+        <v>1249.0</v>
       </c>
       <c r="O191" s="2">
-        <v>685.0</v>
+        <v>728.0</v>
       </c>
       <c r="P191" s="2">
-        <v>461.0</v>
+        <v>480.0</v>
       </c>
       <c r="Q191" s="2">
-        <v>38.0</v>
+        <v>41.0</v>
       </c>
       <c r="R191" s="2">
         <v>47.0</v>
@@ -14012,7 +14012,7 @@
         <v>1326.0</v>
       </c>
       <c r="J193" s="2">
-        <v>1220.0</v>
+        <v>1247.0</v>
       </c>
       <c r="K193" s="2">
         <v>1.0</v>
@@ -14024,16 +14024,16 @@
         <v>0.0</v>
       </c>
       <c r="N193" s="2">
-        <v>1220.0</v>
+        <v>1247.0</v>
       </c>
       <c r="O193" s="2">
-        <v>455.0</v>
+        <v>471.0</v>
       </c>
       <c r="P193" s="2">
-        <v>544.0</v>
+        <v>553.0</v>
       </c>
       <c r="Q193" s="2">
-        <v>221.0</v>
+        <v>223.0</v>
       </c>
       <c r="R193" s="2">
         <v>29.0</v>
@@ -14083,7 +14083,7 @@
         <v>452.0</v>
       </c>
       <c r="J194" s="2">
-        <v>428.0</v>
+        <v>435.0</v>
       </c>
       <c r="K194" s="2">
         <v>1.0</v>
@@ -14095,16 +14095,16 @@
         <v>0.0</v>
       </c>
       <c r="N194" s="2">
-        <v>428.0</v>
+        <v>435.0</v>
       </c>
       <c r="O194" s="2">
-        <v>158.0</v>
+        <v>160.0</v>
       </c>
       <c r="P194" s="2">
         <v>239.0</v>
       </c>
       <c r="Q194" s="2">
-        <v>31.0</v>
+        <v>36.0</v>
       </c>
       <c r="R194" s="2">
         <v>13.0</v>
@@ -14154,7 +14154,7 @@
         <v>556.0</v>
       </c>
       <c r="J195" s="2">
-        <v>521.0</v>
+        <v>538.0</v>
       </c>
       <c r="K195" s="2">
         <v>1.0</v>
@@ -14166,16 +14166,16 @@
         <v>0.0</v>
       </c>
       <c r="N195" s="2">
-        <v>521.0</v>
+        <v>538.0</v>
       </c>
       <c r="O195" s="2">
-        <v>190.0</v>
+        <v>198.0</v>
       </c>
       <c r="P195" s="2">
-        <v>204.0</v>
+        <v>212.0</v>
       </c>
       <c r="Q195" s="2">
-        <v>127.0</v>
+        <v>128.0</v>
       </c>
       <c r="R195" s="2">
         <v>13.0</v>
@@ -14382,10 +14382,10 @@
         <v>1291.0</v>
       </c>
       <c r="O198" s="2">
-        <v>383.0</v>
+        <v>384.0</v>
       </c>
       <c r="P198" s="2">
-        <v>632.0</v>
+        <v>631.0</v>
       </c>
       <c r="Q198" s="2">
         <v>276.0</v>
@@ -14509,7 +14509,7 @@
         <v>704.0</v>
       </c>
       <c r="J200" s="2">
-        <v>614.0</v>
+        <v>632.0</v>
       </c>
       <c r="K200" s="2">
         <v>1.0</v>
@@ -14521,13 +14521,13 @@
         <v>0.0</v>
       </c>
       <c r="N200" s="2">
-        <v>614.0</v>
+        <v>632.0</v>
       </c>
       <c r="O200" s="2">
-        <v>356.0</v>
+        <v>369.0</v>
       </c>
       <c r="P200" s="2">
-        <v>255.0</v>
+        <v>260.0</v>
       </c>
       <c r="Q200" s="2">
         <v>3.0</v>
@@ -14580,7 +14580,7 @@
         <v>1283.0</v>
       </c>
       <c r="J201" s="2">
-        <v>1192.0</v>
+        <v>1195.0</v>
       </c>
       <c r="K201" s="2">
         <v>1.0</v>
@@ -14592,13 +14592,13 @@
         <v>0.0</v>
       </c>
       <c r="N201" s="2">
-        <v>1192.0</v>
+        <v>1195.0</v>
       </c>
       <c r="O201" s="2">
-        <v>632.0</v>
+        <v>634.0</v>
       </c>
       <c r="P201" s="2">
-        <v>548.0</v>
+        <v>549.0</v>
       </c>
       <c r="Q201" s="2">
         <v>12.0</v>
@@ -14607,19 +14607,19 @@
         <v>25.0</v>
       </c>
       <c r="S201" s="2">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="T201" s="2">
         <v>5.0</v>
       </c>
       <c r="U201" s="2">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="V201" s="2">
         <v>1.0</v>
       </c>
       <c r="W201" s="2">
-        <v>71.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="202" ht="15.75" customHeight="1">
@@ -14651,7 +14651,7 @@
         <v>1172.0</v>
       </c>
       <c r="J202" s="2">
-        <v>1038.0</v>
+        <v>1066.0</v>
       </c>
       <c r="K202" s="2">
         <v>1.0</v>
@@ -14663,34 +14663,34 @@
         <v>0.0</v>
       </c>
       <c r="N202" s="2">
-        <v>1038.0</v>
+        <v>1066.0</v>
       </c>
       <c r="O202" s="2">
-        <v>628.0</v>
+        <v>647.0</v>
       </c>
       <c r="P202" s="2">
-        <v>410.0</v>
+        <v>419.0</v>
       </c>
       <c r="Q202" s="2">
         <v>0.0</v>
       </c>
       <c r="R202" s="2">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="S202" s="2">
-        <v>2.0</v>
+        <v>27.0</v>
       </c>
       <c r="T202" s="2">
-        <v>10.0</v>
+        <v>19.0</v>
       </c>
       <c r="U202" s="2">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
       <c r="V202" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="W202" s="2">
-        <v>18.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="203" ht="15.75" customHeight="1">
@@ -14722,7 +14722,7 @@
         <v>1257.0</v>
       </c>
       <c r="J203" s="2">
-        <v>971.0</v>
+        <v>1026.0</v>
       </c>
       <c r="K203" s="2">
         <v>1.0</v>
@@ -14734,25 +14734,25 @@
         <v>0.0</v>
       </c>
       <c r="N203" s="2">
-        <v>971.0</v>
+        <v>1026.0</v>
       </c>
       <c r="O203" s="2">
-        <v>584.0</v>
+        <v>614.0</v>
       </c>
       <c r="P203" s="2">
-        <v>386.0</v>
+        <v>409.0</v>
       </c>
       <c r="Q203" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="R203" s="2">
-        <v>70.0</v>
+        <v>75.0</v>
       </c>
       <c r="S203" s="2">
-        <v>55.0</v>
+        <v>58.0</v>
       </c>
       <c r="T203" s="2">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="U203" s="2">
         <v>0.0</v>
@@ -14761,7 +14761,7 @@
         <v>0.0</v>
       </c>
       <c r="W203" s="2">
-        <v>130.0</v>
+        <v>141.0</v>
       </c>
     </row>
     <row r="204" ht="15.75" customHeight="1">
@@ -14793,7 +14793,7 @@
         <v>1235.0</v>
       </c>
       <c r="J204" s="2">
-        <v>1019.0</v>
+        <v>1050.0</v>
       </c>
       <c r="K204" s="2">
         <v>1.0</v>
@@ -14805,13 +14805,13 @@
         <v>0.0</v>
       </c>
       <c r="N204" s="2">
-        <v>1019.0</v>
+        <v>1050.0</v>
       </c>
       <c r="O204" s="2">
-        <v>554.0</v>
+        <v>562.0</v>
       </c>
       <c r="P204" s="2">
-        <v>448.0</v>
+        <v>471.0</v>
       </c>
       <c r="Q204" s="2">
         <v>17.0</v>
@@ -14820,19 +14820,19 @@
         <v>34.0</v>
       </c>
       <c r="S204" s="2">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="T204" s="2">
         <v>0.0</v>
       </c>
       <c r="U204" s="2">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
       <c r="V204" s="2">
         <v>0.0</v>
       </c>
       <c r="W204" s="2">
-        <v>68.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="205" ht="15.75" customHeight="1">
@@ -14864,7 +14864,7 @@
         <v>897.0</v>
       </c>
       <c r="J205" s="2">
-        <v>761.0</v>
+        <v>813.0</v>
       </c>
       <c r="K205" s="2">
         <v>1.0</v>
@@ -14876,25 +14876,25 @@
         <v>0.0</v>
       </c>
       <c r="N205" s="2">
-        <v>761.0</v>
+        <v>813.0</v>
       </c>
       <c r="O205" s="2">
-        <v>410.0</v>
+        <v>443.0</v>
       </c>
       <c r="P205" s="2">
-        <v>303.0</v>
+        <v>320.0</v>
       </c>
       <c r="Q205" s="2">
-        <v>48.0</v>
+        <v>50.0</v>
       </c>
       <c r="R205" s="2">
-        <v>41.0</v>
+        <v>45.0</v>
       </c>
       <c r="S205" s="2">
-        <v>22.0</v>
+        <v>26.0</v>
       </c>
       <c r="T205" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U205" s="2">
         <v>3.0</v>
@@ -14903,7 +14903,7 @@
         <v>0.0</v>
       </c>
       <c r="W205" s="2">
-        <v>66.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="206" ht="15.75" customHeight="1">
@@ -14935,7 +14935,7 @@
         <v>859.0</v>
       </c>
       <c r="J206" s="2">
-        <v>795.0</v>
+        <v>810.0</v>
       </c>
       <c r="K206" s="2">
         <v>1.0</v>
@@ -14947,13 +14947,13 @@
         <v>0.0</v>
       </c>
       <c r="N206" s="2">
-        <v>795.0</v>
+        <v>810.0</v>
       </c>
       <c r="O206" s="2">
-        <v>510.0</v>
+        <v>521.0</v>
       </c>
       <c r="P206" s="2">
-        <v>285.0</v>
+        <v>289.0</v>
       </c>
       <c r="Q206" s="2">
         <v>0.0</v>
@@ -14962,7 +14962,7 @@
         <v>32.0</v>
       </c>
       <c r="S206" s="2">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="T206" s="2">
         <v>0.0</v>
@@ -14974,7 +14974,7 @@
         <v>0.0</v>
       </c>
       <c r="W206" s="2">
-        <v>43.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="207" ht="15.75" customHeight="1">
@@ -15006,7 +15006,7 @@
         <v>943.0</v>
       </c>
       <c r="J207" s="2">
-        <v>761.0</v>
+        <v>827.0</v>
       </c>
       <c r="K207" s="2">
         <v>1.0</v>
@@ -15018,34 +15018,34 @@
         <v>0.0</v>
       </c>
       <c r="N207" s="2">
-        <v>761.0</v>
+        <v>827.0</v>
       </c>
       <c r="O207" s="2">
-        <v>426.0</v>
+        <v>454.0</v>
       </c>
       <c r="P207" s="2">
-        <v>322.0</v>
+        <v>359.0</v>
       </c>
       <c r="Q207" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="R207" s="2">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="S207" s="2">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="T207" s="2">
         <v>0.0</v>
       </c>
       <c r="U207" s="2">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="V207" s="2">
         <v>0.0</v>
       </c>
       <c r="W207" s="2">
-        <v>72.0</v>
+        <v>77.0</v>
       </c>
     </row>
     <row r="208" ht="15.75" customHeight="1">
@@ -15317,10 +15317,10 @@
         <v>88.0</v>
       </c>
       <c r="S211" s="2">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="T211" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="U211" s="2">
         <v>13.0</v>
@@ -15329,7 +15329,7 @@
         <v>1.0</v>
       </c>
       <c r="W211" s="2">
-        <v>154.0</v>
+        <v>156.0</v>
       </c>
     </row>
     <row r="212" ht="15.75" customHeight="1">
@@ -15432,7 +15432,7 @@
         <v>1034.0</v>
       </c>
       <c r="J213" s="2">
-        <v>848.0</v>
+        <v>858.0</v>
       </c>
       <c r="K213" s="2">
         <v>1.0</v>
@@ -15444,13 +15444,13 @@
         <v>0.0</v>
       </c>
       <c r="N213" s="2">
-        <v>848.0</v>
+        <v>858.0</v>
       </c>
       <c r="O213" s="2">
-        <v>486.0</v>
+        <v>494.0</v>
       </c>
       <c r="P213" s="2">
-        <v>362.0</v>
+        <v>364.0</v>
       </c>
       <c r="Q213" s="2">
         <v>0.0</v>
@@ -15459,19 +15459,19 @@
         <v>43.0</v>
       </c>
       <c r="S213" s="2">
-        <v>2.0</v>
+        <v>39.0</v>
       </c>
       <c r="T213" s="2">
         <v>0.0</v>
       </c>
       <c r="U213" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="V213" s="2">
         <v>0.0</v>
       </c>
       <c r="W213" s="2">
-        <v>45.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="214" ht="15.75" customHeight="1">
@@ -15503,7 +15503,7 @@
         <v>1038.0</v>
       </c>
       <c r="J214" s="2">
-        <v>858.0</v>
+        <v>859.0</v>
       </c>
       <c r="K214" s="2">
         <v>1.0</v>
@@ -15515,13 +15515,13 @@
         <v>0.0</v>
       </c>
       <c r="N214" s="2">
-        <v>858.0</v>
+        <v>859.0</v>
       </c>
       <c r="O214" s="2">
         <v>460.0</v>
       </c>
       <c r="P214" s="2">
-        <v>398.0</v>
+        <v>399.0</v>
       </c>
       <c r="Q214" s="2">
         <v>0.0</v>
@@ -15574,7 +15574,7 @@
         <v>1067.0</v>
       </c>
       <c r="J215" s="2">
-        <v>985.0</v>
+        <v>1002.0</v>
       </c>
       <c r="K215" s="2">
         <v>1.0</v>
@@ -15586,16 +15586,16 @@
         <v>0.0</v>
       </c>
       <c r="N215" s="2">
-        <v>985.0</v>
+        <v>1002.0</v>
       </c>
       <c r="O215" s="2">
-        <v>497.0</v>
+        <v>506.0</v>
       </c>
       <c r="P215" s="2">
-        <v>469.0</v>
+        <v>473.0</v>
       </c>
       <c r="Q215" s="2">
-        <v>19.0</v>
+        <v>23.0</v>
       </c>
       <c r="R215" s="2">
         <v>19.0</v>
@@ -15716,7 +15716,7 @@
         <v>1136.0</v>
       </c>
       <c r="J217" s="2">
-        <v>840.0</v>
+        <v>889.0</v>
       </c>
       <c r="K217" s="2">
         <v>1.0</v>
@@ -15728,34 +15728,34 @@
         <v>0.0</v>
       </c>
       <c r="N217" s="2">
-        <v>840.0</v>
+        <v>889.0</v>
       </c>
       <c r="O217" s="2">
-        <v>437.0</v>
+        <v>462.0</v>
       </c>
       <c r="P217" s="2">
-        <v>403.0</v>
+        <v>426.0</v>
       </c>
       <c r="Q217" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R217" s="2">
         <v>38.0</v>
       </c>
       <c r="S217" s="2">
-        <v>47.0</v>
+        <v>51.0</v>
       </c>
       <c r="T217" s="2">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="U217" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="V217" s="2">
         <v>0.0</v>
       </c>
       <c r="W217" s="2">
-        <v>94.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="218" ht="15.75" customHeight="1">
@@ -15787,7 +15787,7 @@
         <v>1197.0</v>
       </c>
       <c r="J218" s="2">
-        <v>881.0</v>
+        <v>981.0</v>
       </c>
       <c r="K218" s="2">
         <v>1.0</v>
@@ -15799,13 +15799,13 @@
         <v>1.0</v>
       </c>
       <c r="N218" s="2">
-        <v>880.0</v>
+        <v>980.0</v>
       </c>
       <c r="O218" s="2">
-        <v>458.0</v>
+        <v>496.0</v>
       </c>
       <c r="P218" s="2">
-        <v>423.0</v>
+        <v>485.0</v>
       </c>
       <c r="Q218" s="2">
         <v>0.0</v>
@@ -15814,19 +15814,19 @@
         <v>52.0</v>
       </c>
       <c r="S218" s="2">
-        <v>18.0</v>
+        <v>35.0</v>
       </c>
       <c r="T218" s="2">
         <v>9.0</v>
       </c>
       <c r="U218" s="2">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="V218" s="2">
         <v>0.0</v>
       </c>
       <c r="W218" s="2">
-        <v>82.0</v>
+        <v>103.0</v>
       </c>
     </row>
     <row r="219" ht="15.75" customHeight="1">
@@ -15858,7 +15858,7 @@
         <v>1433.0</v>
       </c>
       <c r="J219" s="2">
-        <v>1151.0</v>
+        <v>1191.0</v>
       </c>
       <c r="K219" s="2">
         <v>1.0</v>
@@ -15870,19 +15870,19 @@
         <v>0.0</v>
       </c>
       <c r="N219" s="2">
-        <v>1151.0</v>
+        <v>1191.0</v>
       </c>
       <c r="O219" s="2">
-        <v>277.0</v>
+        <v>299.0</v>
       </c>
       <c r="P219" s="2">
-        <v>491.0</v>
+        <v>509.0</v>
       </c>
       <c r="Q219" s="2">
         <v>383.0</v>
       </c>
       <c r="R219" s="2">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="S219" s="2">
         <v>62.0</v>
@@ -15897,7 +15897,7 @@
         <v>0.0</v>
       </c>
       <c r="W219" s="2">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="220" ht="15.75" customHeight="1">
@@ -15929,7 +15929,7 @@
         <v>867.0</v>
       </c>
       <c r="J220" s="2">
-        <v>743.0</v>
+        <v>767.0</v>
       </c>
       <c r="K220" s="2">
         <v>1.0</v>
@@ -15941,22 +15941,22 @@
         <v>0.0</v>
       </c>
       <c r="N220" s="2">
-        <v>743.0</v>
+        <v>767.0</v>
       </c>
       <c r="O220" s="2">
-        <v>174.0</v>
+        <v>188.0</v>
       </c>
       <c r="P220" s="2">
-        <v>336.0</v>
+        <v>344.0</v>
       </c>
       <c r="Q220" s="2">
-        <v>233.0</v>
+        <v>235.0</v>
       </c>
       <c r="R220" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="S220" s="2">
-        <v>82.0</v>
+        <v>83.0</v>
       </c>
       <c r="T220" s="2">
         <v>1.0</v>
@@ -15968,7 +15968,7 @@
         <v>0.0</v>
       </c>
       <c r="W220" s="2">
-        <v>98.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="221" ht="15.75" customHeight="1">
@@ -16071,7 +16071,7 @@
         <v>1043.0</v>
       </c>
       <c r="J222" s="2">
-        <v>987.0</v>
+        <v>1006.0</v>
       </c>
       <c r="K222" s="2">
         <v>1.0</v>
@@ -16083,22 +16083,22 @@
         <v>0.0</v>
       </c>
       <c r="N222" s="2">
-        <v>987.0</v>
+        <v>1006.0</v>
       </c>
       <c r="O222" s="2">
-        <v>304.0</v>
+        <v>312.0</v>
       </c>
       <c r="P222" s="2">
-        <v>432.0</v>
+        <v>442.0</v>
       </c>
       <c r="Q222" s="2">
-        <v>251.0</v>
+        <v>252.0</v>
       </c>
       <c r="R222" s="2">
-        <v>12.0</v>
+        <v>17.0</v>
       </c>
       <c r="S222" s="2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="T222" s="2">
         <v>0.0</v>
@@ -16110,7 +16110,7 @@
         <v>0.0</v>
       </c>
       <c r="W222" s="2">
-        <v>12.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="223" ht="15.75" customHeight="1">
@@ -16142,7 +16142,7 @@
         <v>1272.0</v>
       </c>
       <c r="J223" s="2">
-        <v>935.0</v>
+        <v>1023.0</v>
       </c>
       <c r="K223" s="2">
         <v>1.0</v>
@@ -16154,7 +16154,7 @@
         <v>0.0</v>
       </c>
       <c r="N223" s="2">
-        <v>935.0</v>
+        <v>1023.0</v>
       </c>
       <c r="O223" s="2">
         <v>115.0</v>
@@ -16163,16 +16163,16 @@
         <v>287.0</v>
       </c>
       <c r="Q223" s="2">
-        <v>533.0</v>
+        <v>621.0</v>
       </c>
       <c r="R223" s="2">
-        <v>72.0</v>
+        <v>74.0</v>
       </c>
       <c r="S223" s="2">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
       <c r="T223" s="2">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
       <c r="U223" s="2">
         <v>0.0</v>
@@ -16181,7 +16181,7 @@
         <v>0.0</v>
       </c>
       <c r="W223" s="2">
-        <v>109.0</v>
+        <v>119.0</v>
       </c>
     </row>
     <row r="224" ht="15.75" customHeight="1">
@@ -16213,7 +16213,7 @@
         <v>766.0</v>
       </c>
       <c r="J224" s="2">
-        <v>649.0</v>
+        <v>698.0</v>
       </c>
       <c r="K224" s="2">
         <v>1.0</v>
@@ -16225,7 +16225,7 @@
         <v>0.0</v>
       </c>
       <c r="N224" s="2">
-        <v>649.0</v>
+        <v>698.0</v>
       </c>
       <c r="O224" s="2">
         <v>22.0</v>
@@ -16234,13 +16234,13 @@
         <v>38.0</v>
       </c>
       <c r="Q224" s="2">
-        <v>589.0</v>
+        <v>638.0</v>
       </c>
       <c r="R224" s="2">
-        <v>23.0</v>
+        <v>26.0</v>
       </c>
       <c r="S224" s="2">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="T224" s="2">
         <v>0.0</v>
@@ -16252,7 +16252,7 @@
         <v>0.0</v>
       </c>
       <c r="W224" s="2">
-        <v>23.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="225" ht="15.75" customHeight="1">
@@ -16355,7 +16355,7 @@
         <v>1256.0</v>
       </c>
       <c r="J226" s="2">
-        <v>922.0</v>
+        <v>936.0</v>
       </c>
       <c r="K226" s="2">
         <v>1.0</v>
@@ -16367,22 +16367,22 @@
         <v>0.0</v>
       </c>
       <c r="N226" s="2">
-        <v>922.0</v>
+        <v>936.0</v>
       </c>
       <c r="O226" s="2">
-        <v>183.0</v>
+        <v>194.0</v>
       </c>
       <c r="P226" s="2">
-        <v>412.0</v>
+        <v>413.0</v>
       </c>
       <c r="Q226" s="2">
-        <v>327.0</v>
+        <v>329.0</v>
       </c>
       <c r="R226" s="2">
         <v>138.0</v>
       </c>
       <c r="S226" s="2">
-        <v>38.0</v>
+        <v>44.0</v>
       </c>
       <c r="T226" s="2">
         <v>0.0</v>
@@ -16394,7 +16394,7 @@
         <v>0.0</v>
       </c>
       <c r="W226" s="2">
-        <v>176.0</v>
+        <v>182.0</v>
       </c>
     </row>
     <row r="227" ht="15.75" customHeight="1">
@@ -16426,7 +16426,7 @@
         <v>428.0</v>
       </c>
       <c r="J227" s="2">
-        <v>372.0</v>
+        <v>387.0</v>
       </c>
       <c r="K227" s="2">
         <v>1.0</v>
@@ -16438,13 +16438,13 @@
         <v>0.0</v>
       </c>
       <c r="N227" s="2">
-        <v>372.0</v>
+        <v>387.0</v>
       </c>
       <c r="O227" s="2">
-        <v>236.0</v>
+        <v>247.0</v>
       </c>
       <c r="P227" s="2">
-        <v>136.0</v>
+        <v>140.0</v>
       </c>
       <c r="Q227" s="2">
         <v>0.0</v>
@@ -16497,7 +16497,7 @@
         <v>1402.0</v>
       </c>
       <c r="J228" s="2">
-        <v>1096.0</v>
+        <v>1146.0</v>
       </c>
       <c r="K228" s="2">
         <v>1.0</v>
@@ -16509,22 +16509,22 @@
         <v>0.0</v>
       </c>
       <c r="N228" s="2">
-        <v>1096.0</v>
+        <v>1146.0</v>
       </c>
       <c r="O228" s="2">
-        <v>329.0</v>
+        <v>363.0</v>
       </c>
       <c r="P228" s="2">
-        <v>433.0</v>
+        <v>446.0</v>
       </c>
       <c r="Q228" s="2">
-        <v>334.0</v>
+        <v>337.0</v>
       </c>
       <c r="R228" s="2">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="S228" s="2">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="T228" s="2">
         <v>0.0</v>
@@ -16536,7 +16536,7 @@
         <v>0.0</v>
       </c>
       <c r="W228" s="2">
-        <v>46.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="229" ht="15.75" customHeight="1">
@@ -16568,7 +16568,7 @@
         <v>832.0</v>
       </c>
       <c r="J229" s="2">
-        <v>784.0</v>
+        <v>786.0</v>
       </c>
       <c r="K229" s="2">
         <v>1.0</v>
@@ -16580,16 +16580,16 @@
         <v>0.0</v>
       </c>
       <c r="N229" s="2">
-        <v>784.0</v>
+        <v>786.0</v>
       </c>
       <c r="O229" s="2">
-        <v>447.0</v>
+        <v>448.0</v>
       </c>
       <c r="P229" s="2">
         <v>336.0</v>
       </c>
       <c r="Q229" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R229" s="2">
         <v>19.0</v>
@@ -16639,7 +16639,7 @@
         <v>934.0</v>
       </c>
       <c r="J230" s="2">
-        <v>743.0</v>
+        <v>744.0</v>
       </c>
       <c r="K230" s="2">
         <v>1.0</v>
@@ -16651,10 +16651,10 @@
         <v>0.0</v>
       </c>
       <c r="N230" s="2">
-        <v>743.0</v>
+        <v>744.0</v>
       </c>
       <c r="O230" s="2">
-        <v>249.0</v>
+        <v>250.0</v>
       </c>
       <c r="P230" s="2">
         <v>301.0</v>
@@ -16663,10 +16663,10 @@
         <v>193.0</v>
       </c>
       <c r="R230" s="2">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="S230" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T230" s="2">
         <v>0.0</v>
@@ -16678,7 +16678,7 @@
         <v>0.0</v>
       </c>
       <c r="W230" s="2">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="231" ht="15.75" customHeight="1">
@@ -16710,7 +16710,7 @@
         <v>1070.0</v>
       </c>
       <c r="J231" s="2">
-        <v>902.0</v>
+        <v>920.0</v>
       </c>
       <c r="K231" s="2">
         <v>1.0</v>
@@ -16722,13 +16722,13 @@
         <v>0.0</v>
       </c>
       <c r="N231" s="2">
-        <v>902.0</v>
+        <v>920.0</v>
       </c>
       <c r="O231" s="2">
-        <v>481.0</v>
+        <v>492.0</v>
       </c>
       <c r="P231" s="2">
-        <v>398.0</v>
+        <v>405.0</v>
       </c>
       <c r="Q231" s="2">
         <v>23.0</v>
@@ -16737,10 +16737,10 @@
         <v>14.0</v>
       </c>
       <c r="S231" s="2">
-        <v>124.0</v>
+        <v>128.0</v>
       </c>
       <c r="T231" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="U231" s="2">
         <v>3.0</v>
@@ -16749,7 +16749,7 @@
         <v>0.0</v>
       </c>
       <c r="W231" s="2">
-        <v>143.0</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="232" ht="15.75" customHeight="1">
@@ -16781,7 +16781,7 @@
         <v>1369.0</v>
       </c>
       <c r="J232" s="2">
-        <v>1045.0</v>
+        <v>1065.0</v>
       </c>
       <c r="K232" s="2">
         <v>1.0</v>
@@ -16793,22 +16793,22 @@
         <v>0.0</v>
       </c>
       <c r="N232" s="2">
-        <v>1045.0</v>
+        <v>1065.0</v>
       </c>
       <c r="O232" s="2">
-        <v>175.0</v>
+        <v>176.0</v>
       </c>
       <c r="P232" s="2">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="Q232" s="2">
-        <v>648.0</v>
+        <v>666.0</v>
       </c>
       <c r="R232" s="2">
-        <v>35.0</v>
+        <v>54.0</v>
       </c>
       <c r="S232" s="2">
-        <v>62.0</v>
+        <v>88.0</v>
       </c>
       <c r="T232" s="2">
         <v>0.0</v>
@@ -16820,7 +16820,7 @@
         <v>0.0</v>
       </c>
       <c r="W232" s="2">
-        <v>97.0</v>
+        <v>142.0</v>
       </c>
     </row>
     <row r="233" ht="15.75" customHeight="1">
